--- a/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>CNI</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>12437000</v>
+        <v>12435700</v>
       </c>
       <c r="E8" s="3">
-        <v>10524900</v>
+        <v>12641900</v>
       </c>
       <c r="F8" s="3">
-        <v>10046600</v>
+        <v>10698400</v>
       </c>
       <c r="G8" s="3">
-        <v>10844800</v>
+        <v>10212100</v>
       </c>
       <c r="H8" s="3">
-        <v>10411500</v>
+        <v>11023500</v>
       </c>
       <c r="I8" s="3">
-        <v>9480900</v>
+        <v>10583100</v>
       </c>
       <c r="J8" s="3">
+        <v>9637200</v>
+      </c>
+      <c r="K8" s="3">
         <v>8751000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9469100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9525800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8140800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7382600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6935600</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3423500</v>
+        <v>3215300</v>
       </c>
       <c r="E9" s="3">
-        <v>2613600</v>
+        <v>3479900</v>
       </c>
       <c r="F9" s="3">
-        <v>2402000</v>
+        <v>2656700</v>
       </c>
       <c r="G9" s="3">
-        <v>2838200</v>
+        <v>2441600</v>
       </c>
       <c r="H9" s="3">
-        <v>2692100</v>
+        <v>2885000</v>
       </c>
       <c r="I9" s="3">
-        <v>2276300</v>
+        <v>2736500</v>
       </c>
       <c r="J9" s="3">
+        <v>2313800</v>
+      </c>
+      <c r="K9" s="3">
         <v>1921500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2263100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2703700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2286400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2063000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1945200</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9013500</v>
+        <v>9220400</v>
       </c>
       <c r="E10" s="3">
-        <v>7911300</v>
+        <v>9162000</v>
       </c>
       <c r="F10" s="3">
-        <v>7644500</v>
+        <v>8041700</v>
       </c>
       <c r="G10" s="3">
-        <v>8006600</v>
+        <v>7770500</v>
       </c>
       <c r="H10" s="3">
-        <v>7719400</v>
+        <v>8138500</v>
       </c>
       <c r="I10" s="3">
-        <v>7204700</v>
+        <v>7846600</v>
       </c>
       <c r="J10" s="3">
+        <v>7323400</v>
+      </c>
+      <c r="K10" s="3">
         <v>6829500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7206000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6822100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5854500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5319600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4990400</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -954,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>-583100</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-592700</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -974,8 +993,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -986,51 +1005,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1257000</v>
+        <v>1342700</v>
       </c>
       <c r="E15" s="3">
-        <v>1161800</v>
+        <v>1277700</v>
       </c>
       <c r="F15" s="3">
-        <v>1155200</v>
+        <v>1180900</v>
       </c>
       <c r="G15" s="3">
-        <v>1135600</v>
+        <v>1174300</v>
       </c>
       <c r="H15" s="3">
-        <v>966200</v>
+        <v>1154300</v>
       </c>
       <c r="I15" s="3">
-        <v>931300</v>
+        <v>982100</v>
       </c>
       <c r="J15" s="3">
+        <v>946600</v>
+      </c>
+      <c r="K15" s="3">
         <v>890600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>869500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>824300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>754400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>687700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>679100</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7464200</v>
+        <v>7560600</v>
       </c>
       <c r="E17" s="3">
-        <v>5797900</v>
+        <v>7587200</v>
       </c>
       <c r="F17" s="3">
-        <v>6573600</v>
+        <v>5893400</v>
       </c>
       <c r="G17" s="3">
-        <v>6778600</v>
+        <v>6681900</v>
       </c>
       <c r="H17" s="3">
-        <v>6418000</v>
+        <v>6890300</v>
       </c>
       <c r="I17" s="3">
-        <v>5669200</v>
+        <v>6523800</v>
       </c>
       <c r="J17" s="3">
+        <v>5762600</v>
+      </c>
+      <c r="K17" s="3">
         <v>5092700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5515100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5895700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5159300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4640100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4403500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4972700</v>
+        <v>4875100</v>
       </c>
       <c r="E18" s="3">
-        <v>4727000</v>
+        <v>5054700</v>
       </c>
       <c r="F18" s="3">
-        <v>3472900</v>
+        <v>4804900</v>
       </c>
       <c r="G18" s="3">
-        <v>4066200</v>
+        <v>3530200</v>
       </c>
       <c r="H18" s="3">
-        <v>3993500</v>
+        <v>4133200</v>
       </c>
       <c r="I18" s="3">
-        <v>3811700</v>
+        <v>4059300</v>
       </c>
       <c r="J18" s="3">
+        <v>3874500</v>
+      </c>
+      <c r="K18" s="3">
         <v>3658300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3954000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3630100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2981500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2742400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2532100</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>342400</v>
+        <v>453000</v>
       </c>
       <c r="E20" s="3">
-        <v>320600</v>
+        <v>348100</v>
       </c>
       <c r="F20" s="3">
-        <v>233400</v>
+        <v>325900</v>
       </c>
       <c r="G20" s="3">
-        <v>271900</v>
+        <v>237200</v>
       </c>
       <c r="H20" s="3">
-        <v>492900</v>
+        <v>276400</v>
       </c>
       <c r="I20" s="3">
-        <v>237700</v>
+        <v>501000</v>
       </c>
       <c r="J20" s="3">
+        <v>241600</v>
+      </c>
+      <c r="K20" s="3">
         <v>272600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>35300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>84000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>56200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>234400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>308100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6579200</v>
+        <v>6677100</v>
       </c>
       <c r="E21" s="3">
-        <v>6215900</v>
+        <v>6686500</v>
       </c>
       <c r="F21" s="3">
-        <v>4868000</v>
+        <v>6317200</v>
       </c>
       <c r="G21" s="3">
-        <v>5480000</v>
+        <v>4947100</v>
       </c>
       <c r="H21" s="3">
-        <v>5458000</v>
+        <v>5569300</v>
       </c>
       <c r="I21" s="3">
-        <v>4986000</v>
+        <v>5547000</v>
       </c>
       <c r="J21" s="3">
+        <v>5067300</v>
+      </c>
+      <c r="K21" s="3">
         <v>4826500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4845500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4535300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3790800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3665900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3522500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>398400</v>
+        <v>533600</v>
       </c>
       <c r="E22" s="3">
-        <v>443500</v>
+        <v>405000</v>
       </c>
       <c r="F22" s="3">
-        <v>402800</v>
+        <v>450800</v>
       </c>
       <c r="G22" s="3">
-        <v>391100</v>
+        <v>409400</v>
       </c>
       <c r="H22" s="3">
+        <v>397600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>361400</v>
+      </c>
+      <c r="J22" s="3">
         <v>355500</v>
       </c>
-      <c r="I22" s="3">
-        <v>349700</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>349000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>329600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>291300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>274800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>254500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>262000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4916800</v>
+        <v>4794600</v>
       </c>
       <c r="E23" s="3">
-        <v>4604200</v>
+        <v>4997800</v>
       </c>
       <c r="F23" s="3">
-        <v>3303500</v>
+        <v>4680000</v>
       </c>
       <c r="G23" s="3">
-        <v>3946900</v>
+        <v>3358000</v>
       </c>
       <c r="H23" s="3">
-        <v>4130900</v>
+        <v>4012000</v>
       </c>
       <c r="I23" s="3">
-        <v>3699800</v>
+        <v>4198900</v>
       </c>
       <c r="J23" s="3">
+        <v>3760700</v>
+      </c>
+      <c r="K23" s="3">
         <v>3582000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3659700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3422800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2762900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2722300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2578200</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1195900</v>
+        <v>637700</v>
       </c>
       <c r="E24" s="3">
-        <v>1047600</v>
+        <v>1215600</v>
       </c>
       <c r="F24" s="3">
-        <v>816400</v>
+        <v>1064900</v>
       </c>
       <c r="G24" s="3">
-        <v>881900</v>
+        <v>829900</v>
       </c>
       <c r="H24" s="3">
-        <v>984400</v>
+        <v>896400</v>
       </c>
       <c r="I24" s="3">
-        <v>-1569600</v>
+        <v>1000600</v>
       </c>
       <c r="J24" s="3">
+        <v>-1595500</v>
+      </c>
+      <c r="K24" s="3">
         <v>935700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1003100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>936600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>752100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>727800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>690600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3720800</v>
+        <v>4156800</v>
       </c>
       <c r="E26" s="3">
-        <v>3556500</v>
+        <v>3782200</v>
       </c>
       <c r="F26" s="3">
-        <v>2487100</v>
+        <v>3615100</v>
       </c>
       <c r="G26" s="3">
-        <v>3065100</v>
+        <v>2528100</v>
       </c>
       <c r="H26" s="3">
-        <v>3146500</v>
+        <v>3115600</v>
       </c>
       <c r="I26" s="3">
-        <v>5269400</v>
+        <v>3198300</v>
       </c>
       <c r="J26" s="3">
+        <v>5356200</v>
+      </c>
+      <c r="K26" s="3">
         <v>2646300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2656500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2486300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2010800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1994500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1887500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3720800</v>
+        <v>4156800</v>
       </c>
       <c r="E27" s="3">
-        <v>3556500</v>
+        <v>3782200</v>
       </c>
       <c r="F27" s="3">
-        <v>2487100</v>
+        <v>3615100</v>
       </c>
       <c r="G27" s="3">
-        <v>3065100</v>
+        <v>2528100</v>
       </c>
       <c r="H27" s="3">
-        <v>3146500</v>
+        <v>3115600</v>
       </c>
       <c r="I27" s="3">
-        <v>5269400</v>
+        <v>3198300</v>
       </c>
       <c r="J27" s="3">
+        <v>5356200</v>
+      </c>
+      <c r="K27" s="3">
         <v>2646300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2656500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2486300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2010800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1994500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1887500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1535,20 +1595,20 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>102500</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="G29" s="3">
+        <v>104200</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
-        <v>-1282400</v>
-      </c>
-      <c r="J29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-1303600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-342400</v>
+        <v>-453000</v>
       </c>
       <c r="E32" s="3">
-        <v>-320600</v>
+        <v>-348100</v>
       </c>
       <c r="F32" s="3">
-        <v>-233400</v>
+        <v>-325900</v>
       </c>
       <c r="G32" s="3">
-        <v>-271900</v>
+        <v>-237200</v>
       </c>
       <c r="H32" s="3">
-        <v>-492900</v>
+        <v>-276400</v>
       </c>
       <c r="I32" s="3">
-        <v>-237700</v>
+        <v>-501000</v>
       </c>
       <c r="J32" s="3">
+        <v>-241600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-272600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-35300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-84000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-56200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-234400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-308100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3720800</v>
+        <v>4156800</v>
       </c>
       <c r="E33" s="3">
-        <v>3556500</v>
+        <v>3782200</v>
       </c>
       <c r="F33" s="3">
-        <v>2589600</v>
+        <v>3615100</v>
       </c>
       <c r="G33" s="3">
-        <v>3065100</v>
+        <v>2632300</v>
       </c>
       <c r="H33" s="3">
-        <v>3146500</v>
+        <v>3115600</v>
       </c>
       <c r="I33" s="3">
-        <v>3986900</v>
+        <v>3198300</v>
       </c>
       <c r="J33" s="3">
+        <v>4052600</v>
+      </c>
+      <c r="K33" s="3">
         <v>2646300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2656500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2486300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2010800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1994500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1887500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3720800</v>
+        <v>4156800</v>
       </c>
       <c r="E35" s="3">
-        <v>3556500</v>
+        <v>3782200</v>
       </c>
       <c r="F35" s="3">
-        <v>2589600</v>
+        <v>3615100</v>
       </c>
       <c r="G35" s="3">
-        <v>3065100</v>
+        <v>2632300</v>
       </c>
       <c r="H35" s="3">
-        <v>3146500</v>
+        <v>3115600</v>
       </c>
       <c r="I35" s="3">
-        <v>3986900</v>
+        <v>3198300</v>
       </c>
       <c r="J35" s="3">
+        <v>4052600</v>
+      </c>
+      <c r="K35" s="3">
         <v>2646300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2656500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2486300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2010800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1994500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1887500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>238500</v>
+        <v>351000</v>
       </c>
       <c r="E41" s="3">
-        <v>609200</v>
+        <v>242400</v>
       </c>
       <c r="F41" s="3">
-        <v>413700</v>
+        <v>619300</v>
       </c>
       <c r="G41" s="3">
-        <v>46500</v>
+        <v>420500</v>
       </c>
       <c r="H41" s="3">
-        <v>193400</v>
+        <v>47300</v>
       </c>
       <c r="I41" s="3">
-        <v>50900</v>
+        <v>196600</v>
       </c>
       <c r="J41" s="3">
+        <v>51700</v>
+      </c>
+      <c r="K41" s="3">
         <v>128000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>114900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>164700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>115400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>77600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,303 +2073,327 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1030200</v>
+        <v>960700</v>
       </c>
       <c r="E43" s="3">
-        <v>780800</v>
+        <v>1047100</v>
       </c>
       <c r="F43" s="3">
-        <v>828100</v>
+        <v>793700</v>
       </c>
       <c r="G43" s="3">
-        <v>881900</v>
+        <v>841700</v>
       </c>
       <c r="H43" s="3">
-        <v>849900</v>
+        <v>896400</v>
       </c>
       <c r="I43" s="3">
-        <v>715400</v>
+        <v>863900</v>
       </c>
       <c r="J43" s="3">
+        <v>727200</v>
+      </c>
+      <c r="K43" s="3">
         <v>636100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>659300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>728500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>627400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>618400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>629900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>503100</v>
+        <v>516600</v>
       </c>
       <c r="E44" s="3">
-        <v>428200</v>
+        <v>511400</v>
       </c>
       <c r="F44" s="3">
-        <v>423800</v>
+        <v>435300</v>
       </c>
       <c r="G44" s="3">
-        <v>444200</v>
+        <v>430800</v>
       </c>
       <c r="H44" s="3">
-        <v>404900</v>
+        <v>451500</v>
       </c>
       <c r="I44" s="3">
-        <v>308300</v>
+        <v>411600</v>
       </c>
       <c r="J44" s="3">
+        <v>313300</v>
+      </c>
+      <c r="K44" s="3">
         <v>258100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>266600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>263000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>210900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>171200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>154400</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>567100</v>
+        <v>454500</v>
       </c>
       <c r="E45" s="3">
-        <v>672500</v>
+        <v>576400</v>
       </c>
       <c r="F45" s="3">
-        <v>589600</v>
+        <v>683600</v>
       </c>
       <c r="G45" s="3">
-        <v>684800</v>
+        <v>599300</v>
       </c>
       <c r="H45" s="3">
-        <v>535100</v>
+        <v>696100</v>
       </c>
       <c r="I45" s="3">
-        <v>517600</v>
+        <v>543900</v>
       </c>
       <c r="J45" s="3">
+        <v>526200</v>
+      </c>
+      <c r="K45" s="3">
         <v>509600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>575900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>660200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>518900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>486000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>557700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2338800</v>
+        <v>2282700</v>
       </c>
       <c r="E46" s="3">
-        <v>2490700</v>
+        <v>2377300</v>
       </c>
       <c r="F46" s="3">
-        <v>2255200</v>
+        <v>2531800</v>
       </c>
       <c r="G46" s="3">
-        <v>2057400</v>
+        <v>2292300</v>
       </c>
       <c r="H46" s="3">
-        <v>1983300</v>
+        <v>2091300</v>
       </c>
       <c r="I46" s="3">
-        <v>1592200</v>
+        <v>2016000</v>
       </c>
       <c r="J46" s="3">
+        <v>1618400</v>
+      </c>
+      <c r="K46" s="3">
         <v>1531800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1616600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1564600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1521900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1390900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1419700</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>86500</v>
+        <v>308900</v>
       </c>
       <c r="E47" s="3">
-        <v>109800</v>
+        <v>87900</v>
       </c>
       <c r="F47" s="3">
-        <v>87200</v>
+        <v>111600</v>
       </c>
       <c r="G47" s="3">
-        <v>83600</v>
+        <v>88700</v>
       </c>
       <c r="H47" s="3">
-        <v>69800</v>
+        <v>85000</v>
       </c>
       <c r="I47" s="3">
-        <v>72000</v>
+        <v>70900</v>
       </c>
       <c r="J47" s="3">
+        <v>73200</v>
+      </c>
+      <c r="K47" s="3">
         <v>73400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>159900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>156200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>136300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>87100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>99100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31993500</v>
+        <v>33284800</v>
       </c>
       <c r="E48" s="3">
-        <v>30260300</v>
+        <v>32520700</v>
       </c>
       <c r="F48" s="3">
-        <v>29446800</v>
+        <v>30759000</v>
       </c>
       <c r="G48" s="3">
-        <v>29217800</v>
+        <v>29932100</v>
       </c>
       <c r="H48" s="3">
-        <v>27461300</v>
+        <v>29699300</v>
       </c>
       <c r="I48" s="3">
-        <v>24855700</v>
+        <v>27913900</v>
       </c>
       <c r="J48" s="3">
+        <v>25265300</v>
+      </c>
+      <c r="K48" s="3">
         <v>24540200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24496100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22384900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20190100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18263700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18373800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>150500</v>
+        <v>148500</v>
       </c>
       <c r="E49" s="3">
-        <v>151900</v>
+        <v>153000</v>
       </c>
       <c r="F49" s="3">
-        <v>156300</v>
+        <v>154400</v>
       </c>
       <c r="G49" s="3">
-        <v>166500</v>
+        <v>158900</v>
       </c>
       <c r="H49" s="3">
-        <v>53100</v>
+        <v>169200</v>
       </c>
       <c r="I49" s="3">
-        <v>45100</v>
+        <v>53900</v>
       </c>
       <c r="J49" s="3">
+        <v>45800</v>
+      </c>
+      <c r="K49" s="3">
         <v>48700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>53300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>48700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>42400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>41500</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2262500</v>
+        <v>2894600</v>
       </c>
       <c r="E52" s="3">
-        <v>2274800</v>
+        <v>2299700</v>
       </c>
       <c r="F52" s="3">
-        <v>627400</v>
+        <v>2312300</v>
       </c>
       <c r="G52" s="3">
-        <v>306100</v>
+        <v>637700</v>
       </c>
       <c r="H52" s="3">
-        <v>395500</v>
+        <v>311100</v>
       </c>
       <c r="I52" s="3">
-        <v>791700</v>
+        <v>402000</v>
       </c>
       <c r="J52" s="3">
+        <v>804800</v>
+      </c>
+      <c r="K52" s="3">
         <v>746600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1006900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>721500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2614300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>55800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>59900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>36831800</v>
+        <v>38919600</v>
       </c>
       <c r="E54" s="3">
-        <v>35287600</v>
+        <v>37438700</v>
       </c>
       <c r="F54" s="3">
-        <v>32573000</v>
+        <v>35869100</v>
       </c>
       <c r="G54" s="3">
-        <v>31831400</v>
+        <v>33109700</v>
       </c>
       <c r="H54" s="3">
-        <v>29963000</v>
+        <v>32355900</v>
       </c>
       <c r="I54" s="3">
-        <v>27356700</v>
+        <v>30456700</v>
       </c>
       <c r="J54" s="3">
+        <v>27807500</v>
+      </c>
+      <c r="K54" s="3">
         <v>26940800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27332800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24875900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23220100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19839900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19994000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>693600</v>
+        <v>715300</v>
       </c>
       <c r="E57" s="3">
-        <v>656500</v>
+        <v>705000</v>
       </c>
       <c r="F57" s="3">
-        <v>567100</v>
+        <v>667300</v>
       </c>
       <c r="G57" s="3">
-        <v>629600</v>
+        <v>576400</v>
       </c>
       <c r="H57" s="3">
-        <v>713900</v>
+        <v>640000</v>
       </c>
       <c r="I57" s="3">
-        <v>1369700</v>
+        <v>725700</v>
       </c>
       <c r="J57" s="3">
+        <v>1392300</v>
+      </c>
+      <c r="K57" s="3">
         <v>1103600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1166800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1451100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>287300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>341900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>768400</v>
+        <v>1729200</v>
       </c>
       <c r="E58" s="3">
-        <v>369300</v>
+        <v>781100</v>
       </c>
       <c r="F58" s="3">
-        <v>661600</v>
+        <v>375400</v>
       </c>
       <c r="G58" s="3">
-        <v>1403100</v>
+        <v>672500</v>
       </c>
       <c r="H58" s="3">
-        <v>860800</v>
+        <v>1426300</v>
       </c>
       <c r="I58" s="3">
-        <v>1512200</v>
+        <v>875000</v>
       </c>
       <c r="J58" s="3">
+        <v>1537100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1082500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1082700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>427100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>786000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>429400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>103700</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1331200</v>
+        <v>1276200</v>
       </c>
       <c r="E59" s="3">
-        <v>1242500</v>
+        <v>1353100</v>
       </c>
       <c r="F59" s="3">
-        <v>1151600</v>
+        <v>1262900</v>
       </c>
       <c r="G59" s="3">
-        <v>1084000</v>
+        <v>1170600</v>
       </c>
       <c r="H59" s="3">
-        <v>969800</v>
+        <v>1101800</v>
       </c>
       <c r="I59" s="3">
-        <v>13800</v>
+        <v>985800</v>
       </c>
       <c r="J59" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>822900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>922800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>871900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2793200</v>
+        <v>3720800</v>
       </c>
       <c r="E60" s="3">
-        <v>2268300</v>
+        <v>2839200</v>
       </c>
       <c r="F60" s="3">
-        <v>2380200</v>
+        <v>2305600</v>
       </c>
       <c r="G60" s="3">
-        <v>3116700</v>
+        <v>2419500</v>
       </c>
       <c r="H60" s="3">
-        <v>2544500</v>
+        <v>3168100</v>
       </c>
       <c r="I60" s="3">
-        <v>2895700</v>
+        <v>2586500</v>
       </c>
       <c r="J60" s="3">
+        <v>2943400</v>
+      </c>
+      <c r="K60" s="3">
         <v>2186800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2251100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1727900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1923000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1639500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1317500</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10448600</v>
+        <v>11922100</v>
       </c>
       <c r="E61" s="3">
-        <v>8707400</v>
+        <v>10620800</v>
       </c>
       <c r="F61" s="3">
-        <v>8721200</v>
+        <v>8850900</v>
       </c>
       <c r="G61" s="3">
-        <v>8626700</v>
+        <v>8864900</v>
       </c>
       <c r="H61" s="3">
-        <v>8277000</v>
+        <v>8768900</v>
       </c>
       <c r="I61" s="3">
-        <v>6359900</v>
+        <v>8413400</v>
       </c>
       <c r="J61" s="3">
+        <v>6464700</v>
+      </c>
+      <c r="K61" s="3">
         <v>6868800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6746500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6145400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5249400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4705600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4948200</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8043600</v>
+        <v>8410400</v>
       </c>
       <c r="E62" s="3">
-        <v>7776800</v>
+        <v>8176200</v>
       </c>
       <c r="F62" s="3">
-        <v>7185000</v>
+        <v>7905000</v>
       </c>
       <c r="G62" s="3">
-        <v>6972000</v>
+        <v>7303400</v>
       </c>
       <c r="H62" s="3">
-        <v>6316300</v>
+        <v>7086900</v>
       </c>
       <c r="I62" s="3">
-        <v>5992000</v>
+        <v>6420300</v>
       </c>
       <c r="J62" s="3">
+        <v>6090800</v>
+      </c>
+      <c r="K62" s="3">
         <v>7095600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7109900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6428000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6886000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5295100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5523600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>21285400</v>
+        <v>24053400</v>
       </c>
       <c r="E66" s="3">
-        <v>18752500</v>
+        <v>21636100</v>
       </c>
       <c r="F66" s="3">
-        <v>18286500</v>
+        <v>19061500</v>
       </c>
       <c r="G66" s="3">
-        <v>18715400</v>
+        <v>18587800</v>
       </c>
       <c r="H66" s="3">
-        <v>17137800</v>
+        <v>19023800</v>
       </c>
       <c r="I66" s="3">
-        <v>15247600</v>
+        <v>17420200</v>
       </c>
       <c r="J66" s="3">
+        <v>15498800</v>
+      </c>
+      <c r="K66" s="3">
         <v>16151300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16107400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14301300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13248600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11640200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11789300</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>14197800</v>
+        <v>13785900</v>
       </c>
       <c r="E72" s="3">
-        <v>15078900</v>
+        <v>14431700</v>
       </c>
       <c r="F72" s="3">
-        <v>13930200</v>
+        <v>15327400</v>
       </c>
       <c r="G72" s="3">
-        <v>12820100</v>
+        <v>14159800</v>
       </c>
       <c r="H72" s="3">
-        <v>12085100</v>
+        <v>13031300</v>
       </c>
       <c r="I72" s="3">
-        <v>11331200</v>
+        <v>12284200</v>
       </c>
       <c r="J72" s="3">
+        <v>11517900</v>
+      </c>
+      <c r="K72" s="3">
         <v>9627100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9488600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9216500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8304800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7566400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7204500</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15546400</v>
+        <v>14866300</v>
       </c>
       <c r="E76" s="3">
-        <v>16535100</v>
+        <v>15802600</v>
       </c>
       <c r="F76" s="3">
-        <v>14286500</v>
+        <v>16807600</v>
       </c>
       <c r="G76" s="3">
-        <v>13116000</v>
+        <v>14521900</v>
       </c>
       <c r="H76" s="3">
-        <v>12825200</v>
+        <v>13332100</v>
       </c>
       <c r="I76" s="3">
-        <v>12109100</v>
+        <v>13036500</v>
       </c>
       <c r="J76" s="3">
+        <v>12308600</v>
+      </c>
+      <c r="K76" s="3">
         <v>10789600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11225400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10574600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9971500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8199700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8204700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3720800</v>
+        <v>4156800</v>
       </c>
       <c r="E81" s="3">
-        <v>3556500</v>
+        <v>3782200</v>
       </c>
       <c r="F81" s="3">
-        <v>2589600</v>
+        <v>3615100</v>
       </c>
       <c r="G81" s="3">
-        <v>3065100</v>
+        <v>2632300</v>
       </c>
       <c r="H81" s="3">
-        <v>3146500</v>
+        <v>3115600</v>
       </c>
       <c r="I81" s="3">
-        <v>3986900</v>
+        <v>3198300</v>
       </c>
       <c r="J81" s="3">
+        <v>4052600</v>
+      </c>
+      <c r="K81" s="3">
         <v>2646300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2656500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2486300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2010800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1994500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1887500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1257000</v>
+        <v>1342700</v>
       </c>
       <c r="E83" s="3">
-        <v>1161800</v>
+        <v>1277700</v>
       </c>
       <c r="F83" s="3">
-        <v>1155200</v>
+        <v>1180900</v>
       </c>
       <c r="G83" s="3">
-        <v>1135600</v>
+        <v>1174300</v>
       </c>
       <c r="H83" s="3">
-        <v>966200</v>
+        <v>1154300</v>
       </c>
       <c r="I83" s="3">
-        <v>931300</v>
+        <v>982100</v>
       </c>
       <c r="J83" s="3">
+        <v>946600</v>
+      </c>
+      <c r="K83" s="3">
         <v>890600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>869500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>824300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>754400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>687700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>679100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4847000</v>
+        <v>5147100</v>
       </c>
       <c r="E89" s="3">
-        <v>5068000</v>
+        <v>4926800</v>
       </c>
       <c r="F89" s="3">
-        <v>4482000</v>
+        <v>5151500</v>
       </c>
       <c r="G89" s="3">
-        <v>4306100</v>
+        <v>4555900</v>
       </c>
       <c r="H89" s="3">
-        <v>4302400</v>
+        <v>4377000</v>
       </c>
       <c r="I89" s="3">
-        <v>4010200</v>
+        <v>4373300</v>
       </c>
       <c r="J89" s="3">
+        <v>4076300</v>
+      </c>
+      <c r="K89" s="3">
         <v>3781900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3859400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3439300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2731300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2277300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2286300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1999300</v>
+        <v>-2355200</v>
       </c>
       <c r="E91" s="3">
-        <v>-2101800</v>
+        <v>-2032200</v>
       </c>
       <c r="F91" s="3">
-        <v>-2081400</v>
+        <v>-2136400</v>
       </c>
       <c r="G91" s="3">
-        <v>-2809900</v>
+        <v>-2115700</v>
       </c>
       <c r="H91" s="3">
-        <v>-2567100</v>
+        <v>-2856200</v>
       </c>
       <c r="I91" s="3">
-        <v>-1943300</v>
+        <v>-2609400</v>
       </c>
       <c r="J91" s="3">
+        <v>-1975300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1959300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2031800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1803300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1518900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1288200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1248400</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1824800</v>
+        <v>-2562800</v>
       </c>
       <c r="E94" s="3">
-        <v>-2088700</v>
+        <v>-1854900</v>
       </c>
       <c r="F94" s="3">
-        <v>-2141800</v>
+        <v>-2123100</v>
       </c>
       <c r="G94" s="3">
-        <v>-3046200</v>
+        <v>-2177100</v>
       </c>
       <c r="H94" s="3">
-        <v>-2474700</v>
+        <v>-3096400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1990600</v>
+        <v>-2515500</v>
       </c>
       <c r="J94" s="3">
+        <v>-2023400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1949800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2122700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1708300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1425700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1057500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1328300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1456900</v>
+        <v>-1530400</v>
       </c>
       <c r="E96" s="3">
-        <v>-1265000</v>
+        <v>-1480900</v>
       </c>
       <c r="F96" s="3">
-        <v>-1187900</v>
+        <v>-1285800</v>
       </c>
       <c r="G96" s="3">
-        <v>-1122500</v>
+        <v>-1207500</v>
       </c>
       <c r="H96" s="3">
-        <v>-969100</v>
+        <v>-1141000</v>
       </c>
       <c r="I96" s="3">
-        <v>-900800</v>
+        <v>-985100</v>
       </c>
       <c r="J96" s="3">
+        <v>-915600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-842600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-747900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-642200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-557300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-485200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-449400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3393000</v>
+        <v>-2517000</v>
       </c>
       <c r="E100" s="3">
-        <v>-2804100</v>
+        <v>-3448900</v>
       </c>
       <c r="F100" s="3">
-        <v>-1968000</v>
+        <v>-2850300</v>
       </c>
       <c r="G100" s="3">
-        <v>-1383500</v>
+        <v>-2000400</v>
       </c>
       <c r="H100" s="3">
-        <v>-1677900</v>
+        <v>-1406300</v>
       </c>
       <c r="I100" s="3">
-        <v>-2104700</v>
+        <v>-1705600</v>
       </c>
       <c r="J100" s="3">
+        <v>-2139400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1845900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1669200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1860600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1274800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1177300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1267600</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>2200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>10900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-368600</v>
+        <v>66500</v>
       </c>
       <c r="E102" s="3">
-        <v>175200</v>
+        <v>-374700</v>
       </c>
       <c r="F102" s="3">
-        <v>372200</v>
+        <v>178100</v>
       </c>
       <c r="G102" s="3">
-        <v>-124300</v>
+        <v>378400</v>
       </c>
       <c r="H102" s="3">
-        <v>149800</v>
+        <v>-126400</v>
       </c>
       <c r="I102" s="3">
-        <v>-86500</v>
+        <v>152200</v>
       </c>
       <c r="J102" s="3">
+        <v>-87900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>75800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-127200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>45400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>40200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-298800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>12435700</v>
+        <v>12263600</v>
       </c>
       <c r="E8" s="3">
-        <v>12641900</v>
+        <v>12466900</v>
       </c>
       <c r="F8" s="3">
-        <v>10698400</v>
+        <v>10550300</v>
       </c>
       <c r="G8" s="3">
-        <v>10212100</v>
+        <v>10070700</v>
       </c>
       <c r="H8" s="3">
-        <v>11023500</v>
+        <v>10870900</v>
       </c>
       <c r="I8" s="3">
-        <v>10583100</v>
+        <v>10436600</v>
       </c>
       <c r="J8" s="3">
-        <v>9637200</v>
+        <v>9503800</v>
       </c>
       <c r="K8" s="3">
         <v>8751000</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3215300</v>
+        <v>3170800</v>
       </c>
       <c r="E9" s="3">
-        <v>3479900</v>
+        <v>3431700</v>
       </c>
       <c r="F9" s="3">
-        <v>2656700</v>
+        <v>2619900</v>
       </c>
       <c r="G9" s="3">
-        <v>2441600</v>
+        <v>2407800</v>
       </c>
       <c r="H9" s="3">
-        <v>2885000</v>
+        <v>2845100</v>
       </c>
       <c r="I9" s="3">
-        <v>2736500</v>
+        <v>2698600</v>
       </c>
       <c r="J9" s="3">
-        <v>2313800</v>
+        <v>2281700</v>
       </c>
       <c r="K9" s="3">
         <v>1921500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9220400</v>
+        <v>9092700</v>
       </c>
       <c r="E10" s="3">
-        <v>9162000</v>
+        <v>9035200</v>
       </c>
       <c r="F10" s="3">
-        <v>8041700</v>
+        <v>7930400</v>
       </c>
       <c r="G10" s="3">
-        <v>7770500</v>
+        <v>7662900</v>
       </c>
       <c r="H10" s="3">
-        <v>8138500</v>
+        <v>8025800</v>
       </c>
       <c r="I10" s="3">
-        <v>7846600</v>
+        <v>7738000</v>
       </c>
       <c r="J10" s="3">
-        <v>7323400</v>
+        <v>7222000</v>
       </c>
       <c r="K10" s="3">
         <v>6829500</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-592700</v>
+        <v>-584500</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1342700</v>
+        <v>1324200</v>
       </c>
       <c r="E15" s="3">
-        <v>1277700</v>
+        <v>1260000</v>
       </c>
       <c r="F15" s="3">
-        <v>1180900</v>
+        <v>1164600</v>
       </c>
       <c r="G15" s="3">
-        <v>1174300</v>
+        <v>1158000</v>
       </c>
       <c r="H15" s="3">
-        <v>1154300</v>
+        <v>1138300</v>
       </c>
       <c r="I15" s="3">
-        <v>982100</v>
+        <v>968500</v>
       </c>
       <c r="J15" s="3">
-        <v>946600</v>
+        <v>933500</v>
       </c>
       <c r="K15" s="3">
         <v>890600</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7560600</v>
+        <v>7455900</v>
       </c>
       <c r="E17" s="3">
-        <v>7587200</v>
+        <v>7482200</v>
       </c>
       <c r="F17" s="3">
-        <v>5893400</v>
+        <v>5811900</v>
       </c>
       <c r="G17" s="3">
-        <v>6681900</v>
+        <v>6589400</v>
       </c>
       <c r="H17" s="3">
-        <v>6890300</v>
+        <v>6795000</v>
       </c>
       <c r="I17" s="3">
-        <v>6523800</v>
+        <v>6433500</v>
       </c>
       <c r="J17" s="3">
-        <v>5762600</v>
+        <v>5682900</v>
       </c>
       <c r="K17" s="3">
         <v>5092700</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4875100</v>
+        <v>4807600</v>
       </c>
       <c r="E18" s="3">
-        <v>5054700</v>
+        <v>4984700</v>
       </c>
       <c r="F18" s="3">
-        <v>4804900</v>
+        <v>4738400</v>
       </c>
       <c r="G18" s="3">
-        <v>3530200</v>
+        <v>3481300</v>
       </c>
       <c r="H18" s="3">
-        <v>4133200</v>
+        <v>4076000</v>
       </c>
       <c r="I18" s="3">
-        <v>4059300</v>
+        <v>4003100</v>
       </c>
       <c r="J18" s="3">
-        <v>3874500</v>
+        <v>3820900</v>
       </c>
       <c r="K18" s="3">
         <v>3658300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>453000</v>
+        <v>446700</v>
       </c>
       <c r="E20" s="3">
-        <v>348100</v>
+        <v>343200</v>
       </c>
       <c r="F20" s="3">
-        <v>325900</v>
+        <v>321400</v>
       </c>
       <c r="G20" s="3">
-        <v>237200</v>
+        <v>233900</v>
       </c>
       <c r="H20" s="3">
-        <v>276400</v>
+        <v>272600</v>
       </c>
       <c r="I20" s="3">
-        <v>501000</v>
+        <v>494100</v>
       </c>
       <c r="J20" s="3">
-        <v>241600</v>
+        <v>238300</v>
       </c>
       <c r="K20" s="3">
         <v>272600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6677100</v>
+        <v>6575100</v>
       </c>
       <c r="E21" s="3">
-        <v>6686500</v>
+        <v>6584800</v>
       </c>
       <c r="F21" s="3">
-        <v>6317200</v>
+        <v>6221400</v>
       </c>
       <c r="G21" s="3">
-        <v>4947100</v>
+        <v>4870300</v>
       </c>
       <c r="H21" s="3">
-        <v>5569300</v>
+        <v>5483900</v>
       </c>
       <c r="I21" s="3">
-        <v>5547000</v>
+        <v>5463200</v>
       </c>
       <c r="J21" s="3">
-        <v>5067300</v>
+        <v>4990400</v>
       </c>
       <c r="K21" s="3">
         <v>4826500</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>533600</v>
+        <v>526200</v>
       </c>
       <c r="E22" s="3">
-        <v>405000</v>
+        <v>399400</v>
       </c>
       <c r="F22" s="3">
-        <v>450800</v>
+        <v>444500</v>
       </c>
       <c r="G22" s="3">
-        <v>409400</v>
+        <v>403700</v>
       </c>
       <c r="H22" s="3">
-        <v>397600</v>
+        <v>392100</v>
       </c>
       <c r="I22" s="3">
-        <v>361400</v>
+        <v>356400</v>
       </c>
       <c r="J22" s="3">
-        <v>355500</v>
+        <v>350500</v>
       </c>
       <c r="K22" s="3">
         <v>349000</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4794600</v>
+        <v>4728200</v>
       </c>
       <c r="E23" s="3">
-        <v>4997800</v>
+        <v>4928600</v>
       </c>
       <c r="F23" s="3">
-        <v>4680000</v>
+        <v>4615200</v>
       </c>
       <c r="G23" s="3">
-        <v>3358000</v>
+        <v>3311500</v>
       </c>
       <c r="H23" s="3">
-        <v>4012000</v>
+        <v>3956400</v>
       </c>
       <c r="I23" s="3">
-        <v>4198900</v>
+        <v>4140800</v>
       </c>
       <c r="J23" s="3">
-        <v>3760700</v>
+        <v>3708700</v>
       </c>
       <c r="K23" s="3">
         <v>3582000</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>637700</v>
+        <v>628900</v>
       </c>
       <c r="E24" s="3">
-        <v>1215600</v>
+        <v>1198800</v>
       </c>
       <c r="F24" s="3">
-        <v>1064900</v>
+        <v>1050100</v>
       </c>
       <c r="G24" s="3">
-        <v>829900</v>
+        <v>818400</v>
       </c>
       <c r="H24" s="3">
-        <v>896400</v>
+        <v>884000</v>
       </c>
       <c r="I24" s="3">
-        <v>1000600</v>
+        <v>986700</v>
       </c>
       <c r="J24" s="3">
-        <v>-1595500</v>
+        <v>-1573400</v>
       </c>
       <c r="K24" s="3">
         <v>935700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4156800</v>
+        <v>4099300</v>
       </c>
       <c r="E26" s="3">
-        <v>3782200</v>
+        <v>3729800</v>
       </c>
       <c r="F26" s="3">
-        <v>3615100</v>
+        <v>3565100</v>
       </c>
       <c r="G26" s="3">
-        <v>2528100</v>
+        <v>2493100</v>
       </c>
       <c r="H26" s="3">
-        <v>3115600</v>
+        <v>3072500</v>
       </c>
       <c r="I26" s="3">
-        <v>3198300</v>
+        <v>3154100</v>
       </c>
       <c r="J26" s="3">
-        <v>5356200</v>
+        <v>5282100</v>
       </c>
       <c r="K26" s="3">
         <v>2646300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4156800</v>
+        <v>4099300</v>
       </c>
       <c r="E27" s="3">
-        <v>3782200</v>
+        <v>3729800</v>
       </c>
       <c r="F27" s="3">
-        <v>3615100</v>
+        <v>3565100</v>
       </c>
       <c r="G27" s="3">
-        <v>2528100</v>
+        <v>2493100</v>
       </c>
       <c r="H27" s="3">
-        <v>3115600</v>
+        <v>3072500</v>
       </c>
       <c r="I27" s="3">
-        <v>3198300</v>
+        <v>3154100</v>
       </c>
       <c r="J27" s="3">
-        <v>5356200</v>
+        <v>5282100</v>
       </c>
       <c r="K27" s="3">
         <v>2646300</v>
@@ -1599,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="G29" s="3">
-        <v>104200</v>
+        <v>102800</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>8</v>
@@ -1608,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="J29" s="3">
-        <v>-1303600</v>
+        <v>-1285500</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-453000</v>
+        <v>-446700</v>
       </c>
       <c r="E32" s="3">
-        <v>-348100</v>
+        <v>-343200</v>
       </c>
       <c r="F32" s="3">
-        <v>-325900</v>
+        <v>-321400</v>
       </c>
       <c r="G32" s="3">
-        <v>-237200</v>
+        <v>-233900</v>
       </c>
       <c r="H32" s="3">
-        <v>-276400</v>
+        <v>-272600</v>
       </c>
       <c r="I32" s="3">
-        <v>-501000</v>
+        <v>-494100</v>
       </c>
       <c r="J32" s="3">
-        <v>-241600</v>
+        <v>-238300</v>
       </c>
       <c r="K32" s="3">
         <v>-272600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4156800</v>
+        <v>4099300</v>
       </c>
       <c r="E33" s="3">
-        <v>3782200</v>
+        <v>3729800</v>
       </c>
       <c r="F33" s="3">
-        <v>3615100</v>
+        <v>3565100</v>
       </c>
       <c r="G33" s="3">
-        <v>2632300</v>
+        <v>2595800</v>
       </c>
       <c r="H33" s="3">
-        <v>3115600</v>
+        <v>3072500</v>
       </c>
       <c r="I33" s="3">
-        <v>3198300</v>
+        <v>3154100</v>
       </c>
       <c r="J33" s="3">
-        <v>4052600</v>
+        <v>3996500</v>
       </c>
       <c r="K33" s="3">
         <v>2646300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4156800</v>
+        <v>4099300</v>
       </c>
       <c r="E35" s="3">
-        <v>3782200</v>
+        <v>3729800</v>
       </c>
       <c r="F35" s="3">
-        <v>3615100</v>
+        <v>3565100</v>
       </c>
       <c r="G35" s="3">
-        <v>2632300</v>
+        <v>2595800</v>
       </c>
       <c r="H35" s="3">
-        <v>3115600</v>
+        <v>3072500</v>
       </c>
       <c r="I35" s="3">
-        <v>3198300</v>
+        <v>3154100</v>
       </c>
       <c r="J35" s="3">
-        <v>4052600</v>
+        <v>3996500</v>
       </c>
       <c r="K35" s="3">
         <v>2646300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>351000</v>
+        <v>346200</v>
       </c>
       <c r="E41" s="3">
-        <v>242400</v>
+        <v>239000</v>
       </c>
       <c r="F41" s="3">
-        <v>619300</v>
+        <v>610700</v>
       </c>
       <c r="G41" s="3">
-        <v>420500</v>
+        <v>414700</v>
       </c>
       <c r="H41" s="3">
-        <v>47300</v>
+        <v>46600</v>
       </c>
       <c r="I41" s="3">
-        <v>196600</v>
+        <v>193900</v>
       </c>
       <c r="J41" s="3">
-        <v>51700</v>
+        <v>51000</v>
       </c>
       <c r="K41" s="3">
         <v>128000</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>960700</v>
+        <v>947400</v>
       </c>
       <c r="E43" s="3">
-        <v>1047100</v>
+        <v>1032700</v>
       </c>
       <c r="F43" s="3">
-        <v>793700</v>
+        <v>782700</v>
       </c>
       <c r="G43" s="3">
-        <v>841700</v>
+        <v>830100</v>
       </c>
       <c r="H43" s="3">
-        <v>896400</v>
+        <v>884000</v>
       </c>
       <c r="I43" s="3">
-        <v>863900</v>
+        <v>851900</v>
       </c>
       <c r="J43" s="3">
-        <v>727200</v>
+        <v>717100</v>
       </c>
       <c r="K43" s="3">
         <v>636100</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>516600</v>
+        <v>509400</v>
       </c>
       <c r="E44" s="3">
-        <v>511400</v>
+        <v>504300</v>
       </c>
       <c r="F44" s="3">
-        <v>435300</v>
+        <v>429200</v>
       </c>
       <c r="G44" s="3">
-        <v>430800</v>
+        <v>424900</v>
       </c>
       <c r="H44" s="3">
-        <v>451500</v>
+        <v>445300</v>
       </c>
       <c r="I44" s="3">
-        <v>411600</v>
+        <v>405900</v>
       </c>
       <c r="J44" s="3">
-        <v>313300</v>
+        <v>309000</v>
       </c>
       <c r="K44" s="3">
         <v>258100</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>454500</v>
+        <v>448200</v>
       </c>
       <c r="E45" s="3">
-        <v>576400</v>
+        <v>568400</v>
       </c>
       <c r="F45" s="3">
-        <v>683600</v>
+        <v>674100</v>
       </c>
       <c r="G45" s="3">
-        <v>599300</v>
+        <v>591000</v>
       </c>
       <c r="H45" s="3">
-        <v>696100</v>
+        <v>686500</v>
       </c>
       <c r="I45" s="3">
-        <v>543900</v>
+        <v>536400</v>
       </c>
       <c r="J45" s="3">
-        <v>526200</v>
+        <v>518900</v>
       </c>
       <c r="K45" s="3">
         <v>509600</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2282700</v>
+        <v>2251100</v>
       </c>
       <c r="E46" s="3">
-        <v>2377300</v>
+        <v>2344400</v>
       </c>
       <c r="F46" s="3">
-        <v>2531800</v>
+        <v>2496700</v>
       </c>
       <c r="G46" s="3">
-        <v>2292300</v>
+        <v>2260600</v>
       </c>
       <c r="H46" s="3">
-        <v>2091300</v>
+        <v>2062400</v>
       </c>
       <c r="I46" s="3">
-        <v>2016000</v>
+        <v>1988100</v>
       </c>
       <c r="J46" s="3">
-        <v>1618400</v>
+        <v>1596000</v>
       </c>
       <c r="K46" s="3">
         <v>1531800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>308900</v>
+        <v>304600</v>
       </c>
       <c r="E47" s="3">
-        <v>87900</v>
+        <v>86700</v>
       </c>
       <c r="F47" s="3">
-        <v>111600</v>
+        <v>110000</v>
       </c>
       <c r="G47" s="3">
-        <v>88700</v>
+        <v>87500</v>
       </c>
       <c r="H47" s="3">
-        <v>85000</v>
+        <v>83800</v>
       </c>
       <c r="I47" s="3">
-        <v>70900</v>
+        <v>70000</v>
       </c>
       <c r="J47" s="3">
-        <v>73200</v>
+        <v>72100</v>
       </c>
       <c r="K47" s="3">
         <v>73400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>33284800</v>
+        <v>32824100</v>
       </c>
       <c r="E48" s="3">
-        <v>32520700</v>
+        <v>32070500</v>
       </c>
       <c r="F48" s="3">
-        <v>30759000</v>
+        <v>30333200</v>
       </c>
       <c r="G48" s="3">
-        <v>29932100</v>
+        <v>29517700</v>
       </c>
       <c r="H48" s="3">
-        <v>29699300</v>
+        <v>29288100</v>
       </c>
       <c r="I48" s="3">
-        <v>27913900</v>
+        <v>27527500</v>
       </c>
       <c r="J48" s="3">
-        <v>25265300</v>
+        <v>24915600</v>
       </c>
       <c r="K48" s="3">
         <v>24540200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>148500</v>
+        <v>146500</v>
       </c>
       <c r="E49" s="3">
-        <v>153000</v>
+        <v>150900</v>
       </c>
       <c r="F49" s="3">
-        <v>154400</v>
+        <v>152300</v>
       </c>
       <c r="G49" s="3">
-        <v>158900</v>
+        <v>156700</v>
       </c>
       <c r="H49" s="3">
-        <v>169200</v>
+        <v>166900</v>
       </c>
       <c r="I49" s="3">
-        <v>53900</v>
+        <v>53200</v>
       </c>
       <c r="J49" s="3">
-        <v>45800</v>
+        <v>45200</v>
       </c>
       <c r="K49" s="3">
         <v>48700</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2894600</v>
+        <v>2854600</v>
       </c>
       <c r="E52" s="3">
-        <v>2299700</v>
+        <v>2267900</v>
       </c>
       <c r="F52" s="3">
-        <v>2312300</v>
+        <v>2280300</v>
       </c>
       <c r="G52" s="3">
-        <v>637700</v>
+        <v>628900</v>
       </c>
       <c r="H52" s="3">
-        <v>311100</v>
+        <v>306800</v>
       </c>
       <c r="I52" s="3">
-        <v>402000</v>
+        <v>396400</v>
       </c>
       <c r="J52" s="3">
-        <v>804800</v>
+        <v>793600</v>
       </c>
       <c r="K52" s="3">
         <v>746600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>38919600</v>
+        <v>38380900</v>
       </c>
       <c r="E54" s="3">
-        <v>37438700</v>
+        <v>36920400</v>
       </c>
       <c r="F54" s="3">
-        <v>35869100</v>
+        <v>35372600</v>
       </c>
       <c r="G54" s="3">
-        <v>33109700</v>
+        <v>32651400</v>
       </c>
       <c r="H54" s="3">
-        <v>32355900</v>
+        <v>31908000</v>
       </c>
       <c r="I54" s="3">
-        <v>30456700</v>
+        <v>30035100</v>
       </c>
       <c r="J54" s="3">
-        <v>27807500</v>
+        <v>27422500</v>
       </c>
       <c r="K54" s="3">
         <v>26940800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>715300</v>
+        <v>705400</v>
       </c>
       <c r="E57" s="3">
-        <v>705000</v>
+        <v>695200</v>
       </c>
       <c r="F57" s="3">
-        <v>667300</v>
+        <v>658100</v>
       </c>
       <c r="G57" s="3">
-        <v>576400</v>
+        <v>568400</v>
       </c>
       <c r="H57" s="3">
-        <v>640000</v>
+        <v>631100</v>
       </c>
       <c r="I57" s="3">
-        <v>725700</v>
+        <v>715600</v>
       </c>
       <c r="J57" s="3">
-        <v>1392300</v>
+        <v>1373000</v>
       </c>
       <c r="K57" s="3">
         <v>1103600</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1729200</v>
+        <v>1705300</v>
       </c>
       <c r="E58" s="3">
-        <v>781100</v>
+        <v>770300</v>
       </c>
       <c r="F58" s="3">
-        <v>375400</v>
+        <v>370200</v>
       </c>
       <c r="G58" s="3">
-        <v>672500</v>
+        <v>663200</v>
       </c>
       <c r="H58" s="3">
-        <v>1426300</v>
+        <v>1406500</v>
       </c>
       <c r="I58" s="3">
-        <v>875000</v>
+        <v>862900</v>
       </c>
       <c r="J58" s="3">
-        <v>1537100</v>
+        <v>1515800</v>
       </c>
       <c r="K58" s="3">
         <v>1082500</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1276200</v>
+        <v>1258600</v>
       </c>
       <c r="E59" s="3">
-        <v>1353100</v>
+        <v>1334400</v>
       </c>
       <c r="F59" s="3">
-        <v>1262900</v>
+        <v>1245500</v>
       </c>
       <c r="G59" s="3">
-        <v>1170600</v>
+        <v>1154400</v>
       </c>
       <c r="H59" s="3">
-        <v>1101800</v>
+        <v>1086600</v>
       </c>
       <c r="I59" s="3">
-        <v>985800</v>
+        <v>972200</v>
       </c>
       <c r="J59" s="3">
-        <v>14000</v>
+        <v>13800</v>
       </c>
       <c r="K59" s="3">
         <v>700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3720800</v>
+        <v>3669300</v>
       </c>
       <c r="E60" s="3">
-        <v>2839200</v>
+        <v>2799900</v>
       </c>
       <c r="F60" s="3">
-        <v>2305600</v>
+        <v>2273700</v>
       </c>
       <c r="G60" s="3">
-        <v>2419500</v>
+        <v>2386000</v>
       </c>
       <c r="H60" s="3">
-        <v>3168100</v>
+        <v>3124200</v>
       </c>
       <c r="I60" s="3">
-        <v>2586500</v>
+        <v>2550700</v>
       </c>
       <c r="J60" s="3">
-        <v>2943400</v>
+        <v>2902700</v>
       </c>
       <c r="K60" s="3">
         <v>2186800</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11922100</v>
+        <v>11757100</v>
       </c>
       <c r="E61" s="3">
-        <v>10620800</v>
+        <v>10473700</v>
       </c>
       <c r="F61" s="3">
-        <v>8850900</v>
+        <v>8728400</v>
       </c>
       <c r="G61" s="3">
-        <v>8864900</v>
+        <v>8742200</v>
       </c>
       <c r="H61" s="3">
-        <v>8768900</v>
+        <v>8647500</v>
       </c>
       <c r="I61" s="3">
-        <v>8413400</v>
+        <v>8296900</v>
       </c>
       <c r="J61" s="3">
-        <v>6464700</v>
+        <v>6375200</v>
       </c>
       <c r="K61" s="3">
         <v>6868800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8410400</v>
+        <v>8294000</v>
       </c>
       <c r="E62" s="3">
-        <v>8176200</v>
+        <v>8063000</v>
       </c>
       <c r="F62" s="3">
-        <v>7905000</v>
+        <v>7795500</v>
       </c>
       <c r="G62" s="3">
-        <v>7303400</v>
+        <v>7202300</v>
       </c>
       <c r="H62" s="3">
-        <v>7086900</v>
+        <v>6988800</v>
       </c>
       <c r="I62" s="3">
-        <v>6420300</v>
+        <v>6331500</v>
       </c>
       <c r="J62" s="3">
-        <v>6090800</v>
+        <v>6006400</v>
       </c>
       <c r="K62" s="3">
         <v>7095600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>24053400</v>
+        <v>23720400</v>
       </c>
       <c r="E66" s="3">
-        <v>21636100</v>
+        <v>21336600</v>
       </c>
       <c r="F66" s="3">
-        <v>19061500</v>
+        <v>18797600</v>
       </c>
       <c r="G66" s="3">
-        <v>18587800</v>
+        <v>18330500</v>
       </c>
       <c r="H66" s="3">
-        <v>19023800</v>
+        <v>18760500</v>
       </c>
       <c r="I66" s="3">
-        <v>17420200</v>
+        <v>17179100</v>
       </c>
       <c r="J66" s="3">
-        <v>15498800</v>
+        <v>15284300</v>
       </c>
       <c r="K66" s="3">
         <v>16151300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>13785900</v>
+        <v>13595000</v>
       </c>
       <c r="E72" s="3">
-        <v>14431700</v>
+        <v>14232000</v>
       </c>
       <c r="F72" s="3">
-        <v>15327400</v>
+        <v>15115200</v>
       </c>
       <c r="G72" s="3">
-        <v>14159800</v>
+        <v>13963800</v>
       </c>
       <c r="H72" s="3">
-        <v>13031300</v>
+        <v>12851000</v>
       </c>
       <c r="I72" s="3">
-        <v>12284200</v>
+        <v>12114200</v>
       </c>
       <c r="J72" s="3">
-        <v>11517900</v>
+        <v>11358500</v>
       </c>
       <c r="K72" s="3">
         <v>9627100</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14866300</v>
+        <v>14660500</v>
       </c>
       <c r="E76" s="3">
-        <v>15802600</v>
+        <v>15583800</v>
       </c>
       <c r="F76" s="3">
-        <v>16807600</v>
+        <v>16574900</v>
       </c>
       <c r="G76" s="3">
-        <v>14521900</v>
+        <v>14320900</v>
       </c>
       <c r="H76" s="3">
-        <v>13332100</v>
+        <v>13147600</v>
       </c>
       <c r="I76" s="3">
-        <v>13036500</v>
+        <v>12856100</v>
       </c>
       <c r="J76" s="3">
-        <v>12308600</v>
+        <v>12138200</v>
       </c>
       <c r="K76" s="3">
         <v>10789600</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4156800</v>
+        <v>4099300</v>
       </c>
       <c r="E81" s="3">
-        <v>3782200</v>
+        <v>3729800</v>
       </c>
       <c r="F81" s="3">
-        <v>3615100</v>
+        <v>3565100</v>
       </c>
       <c r="G81" s="3">
-        <v>2632300</v>
+        <v>2595800</v>
       </c>
       <c r="H81" s="3">
-        <v>3115600</v>
+        <v>3072500</v>
       </c>
       <c r="I81" s="3">
-        <v>3198300</v>
+        <v>3154100</v>
       </c>
       <c r="J81" s="3">
-        <v>4052600</v>
+        <v>3996500</v>
       </c>
       <c r="K81" s="3">
         <v>2646300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1342700</v>
+        <v>1324200</v>
       </c>
       <c r="E83" s="3">
-        <v>1277700</v>
+        <v>1260000</v>
       </c>
       <c r="F83" s="3">
-        <v>1180900</v>
+        <v>1164600</v>
       </c>
       <c r="G83" s="3">
-        <v>1174300</v>
+        <v>1158000</v>
       </c>
       <c r="H83" s="3">
-        <v>1154300</v>
+        <v>1138300</v>
       </c>
       <c r="I83" s="3">
-        <v>982100</v>
+        <v>968500</v>
       </c>
       <c r="J83" s="3">
-        <v>946600</v>
+        <v>933500</v>
       </c>
       <c r="K83" s="3">
         <v>890600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5147100</v>
+        <v>5075800</v>
       </c>
       <c r="E89" s="3">
-        <v>4926800</v>
+        <v>4858600</v>
       </c>
       <c r="F89" s="3">
-        <v>5151500</v>
+        <v>5080200</v>
       </c>
       <c r="G89" s="3">
-        <v>4555900</v>
+        <v>4492800</v>
       </c>
       <c r="H89" s="3">
-        <v>4377000</v>
+        <v>4316400</v>
       </c>
       <c r="I89" s="3">
-        <v>4373300</v>
+        <v>4312800</v>
       </c>
       <c r="J89" s="3">
-        <v>4076300</v>
+        <v>4019800</v>
       </c>
       <c r="K89" s="3">
         <v>3781900</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2355200</v>
+        <v>-2322600</v>
       </c>
       <c r="E91" s="3">
-        <v>-2032200</v>
+        <v>-2004100</v>
       </c>
       <c r="F91" s="3">
-        <v>-2136400</v>
+        <v>-2106800</v>
       </c>
       <c r="G91" s="3">
-        <v>-2115700</v>
+        <v>-2086400</v>
       </c>
       <c r="H91" s="3">
-        <v>-2856200</v>
+        <v>-2816700</v>
       </c>
       <c r="I91" s="3">
-        <v>-2609400</v>
+        <v>-2573300</v>
       </c>
       <c r="J91" s="3">
-        <v>-1975300</v>
+        <v>-1948000</v>
       </c>
       <c r="K91" s="3">
         <v>-1959300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2562800</v>
+        <v>-2527300</v>
       </c>
       <c r="E94" s="3">
-        <v>-1854900</v>
+        <v>-1829200</v>
       </c>
       <c r="F94" s="3">
-        <v>-2123100</v>
+        <v>-2093700</v>
       </c>
       <c r="G94" s="3">
-        <v>-2177100</v>
+        <v>-2146900</v>
       </c>
       <c r="H94" s="3">
-        <v>-3096400</v>
+        <v>-3053500</v>
       </c>
       <c r="I94" s="3">
-        <v>-2515500</v>
+        <v>-2480700</v>
       </c>
       <c r="J94" s="3">
-        <v>-2023400</v>
+        <v>-1995300</v>
       </c>
       <c r="K94" s="3">
         <v>-1949800</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1530400</v>
+        <v>-1509300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1480900</v>
+        <v>-1460400</v>
       </c>
       <c r="F96" s="3">
-        <v>-1285800</v>
+        <v>-1268000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1207500</v>
+        <v>-1190800</v>
       </c>
       <c r="H96" s="3">
-        <v>-1141000</v>
+        <v>-1125200</v>
       </c>
       <c r="I96" s="3">
-        <v>-985100</v>
+        <v>-971400</v>
       </c>
       <c r="J96" s="3">
-        <v>-915600</v>
+        <v>-902900</v>
       </c>
       <c r="K96" s="3">
         <v>-842600</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2517000</v>
+        <v>-2482200</v>
       </c>
       <c r="E100" s="3">
-        <v>-3448900</v>
+        <v>-3401100</v>
       </c>
       <c r="F100" s="3">
-        <v>-2850300</v>
+        <v>-2810800</v>
       </c>
       <c r="G100" s="3">
-        <v>-2000400</v>
+        <v>-1972800</v>
       </c>
       <c r="H100" s="3">
-        <v>-1406300</v>
+        <v>-1386800</v>
       </c>
       <c r="I100" s="3">
-        <v>-1705600</v>
+        <v>-1682000</v>
       </c>
       <c r="J100" s="3">
-        <v>-2139400</v>
+        <v>-2109800</v>
       </c>
       <c r="K100" s="3">
         <v>-1845900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>66500</v>
+        <v>65600</v>
       </c>
       <c r="E102" s="3">
-        <v>-374700</v>
+        <v>-369500</v>
       </c>
       <c r="F102" s="3">
-        <v>178100</v>
+        <v>175600</v>
       </c>
       <c r="G102" s="3">
-        <v>378400</v>
+        <v>373100</v>
       </c>
       <c r="H102" s="3">
-        <v>-126400</v>
+        <v>-124600</v>
       </c>
       <c r="I102" s="3">
-        <v>152200</v>
+        <v>150100</v>
       </c>
       <c r="J102" s="3">
-        <v>-87900</v>
+        <v>-86700</v>
       </c>
       <c r="K102" s="3">
         <v>-2900</v>

--- a/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>12263600</v>
+        <v>12387300</v>
       </c>
       <c r="E8" s="3">
-        <v>12466900</v>
+        <v>12592600</v>
       </c>
       <c r="F8" s="3">
-        <v>10550300</v>
+        <v>10656700</v>
       </c>
       <c r="G8" s="3">
-        <v>10070700</v>
+        <v>10172300</v>
       </c>
       <c r="H8" s="3">
-        <v>10870900</v>
+        <v>10980600</v>
       </c>
       <c r="I8" s="3">
-        <v>10436600</v>
+        <v>10541800</v>
       </c>
       <c r="J8" s="3">
-        <v>9503800</v>
+        <v>9599600</v>
       </c>
       <c r="K8" s="3">
         <v>8751000</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3170800</v>
+        <v>3202800</v>
       </c>
       <c r="E9" s="3">
-        <v>3431700</v>
+        <v>3466300</v>
       </c>
       <c r="F9" s="3">
-        <v>2619900</v>
+        <v>2646300</v>
       </c>
       <c r="G9" s="3">
-        <v>2407800</v>
+        <v>2432100</v>
       </c>
       <c r="H9" s="3">
-        <v>2845100</v>
+        <v>2873800</v>
       </c>
       <c r="I9" s="3">
-        <v>2698600</v>
+        <v>2725800</v>
       </c>
       <c r="J9" s="3">
-        <v>2281700</v>
+        <v>2304800</v>
       </c>
       <c r="K9" s="3">
         <v>1921500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9092700</v>
+        <v>9184400</v>
       </c>
       <c r="E10" s="3">
-        <v>9035200</v>
+        <v>9126300</v>
       </c>
       <c r="F10" s="3">
-        <v>7930400</v>
+        <v>8010300</v>
       </c>
       <c r="G10" s="3">
-        <v>7662900</v>
+        <v>7740200</v>
       </c>
       <c r="H10" s="3">
-        <v>8025800</v>
+        <v>8106800</v>
       </c>
       <c r="I10" s="3">
-        <v>7738000</v>
+        <v>7816000</v>
       </c>
       <c r="J10" s="3">
-        <v>7222000</v>
+        <v>7294900</v>
       </c>
       <c r="K10" s="3">
         <v>6829500</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-584500</v>
+        <v>-590400</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1324200</v>
+        <v>1337500</v>
       </c>
       <c r="E15" s="3">
-        <v>1260000</v>
+        <v>1272700</v>
       </c>
       <c r="F15" s="3">
-        <v>1164600</v>
+        <v>1176300</v>
       </c>
       <c r="G15" s="3">
-        <v>1158000</v>
+        <v>1169700</v>
       </c>
       <c r="H15" s="3">
-        <v>1138300</v>
+        <v>1149800</v>
       </c>
       <c r="I15" s="3">
-        <v>968500</v>
+        <v>978300</v>
       </c>
       <c r="J15" s="3">
-        <v>933500</v>
+        <v>943000</v>
       </c>
       <c r="K15" s="3">
         <v>890600</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7455900</v>
+        <v>7531100</v>
       </c>
       <c r="E17" s="3">
-        <v>7482200</v>
+        <v>7557600</v>
       </c>
       <c r="F17" s="3">
-        <v>5811900</v>
+        <v>5870500</v>
       </c>
       <c r="G17" s="3">
-        <v>6589400</v>
+        <v>6655900</v>
       </c>
       <c r="H17" s="3">
-        <v>6795000</v>
+        <v>6863500</v>
       </c>
       <c r="I17" s="3">
-        <v>6433500</v>
+        <v>6498400</v>
       </c>
       <c r="J17" s="3">
-        <v>5682900</v>
+        <v>5740200</v>
       </c>
       <c r="K17" s="3">
         <v>5092700</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4807600</v>
+        <v>4856100</v>
       </c>
       <c r="E18" s="3">
-        <v>4984700</v>
+        <v>5035000</v>
       </c>
       <c r="F18" s="3">
-        <v>4738400</v>
+        <v>4786200</v>
       </c>
       <c r="G18" s="3">
-        <v>3481300</v>
+        <v>3516400</v>
       </c>
       <c r="H18" s="3">
-        <v>4076000</v>
+        <v>4117100</v>
       </c>
       <c r="I18" s="3">
-        <v>4003100</v>
+        <v>4043500</v>
       </c>
       <c r="J18" s="3">
-        <v>3820900</v>
+        <v>3859400</v>
       </c>
       <c r="K18" s="3">
         <v>3658300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>446700</v>
+        <v>451200</v>
       </c>
       <c r="E20" s="3">
-        <v>343200</v>
+        <v>346700</v>
       </c>
       <c r="F20" s="3">
-        <v>321400</v>
+        <v>324600</v>
       </c>
       <c r="G20" s="3">
-        <v>233900</v>
+        <v>236300</v>
       </c>
       <c r="H20" s="3">
-        <v>272600</v>
+        <v>275300</v>
       </c>
       <c r="I20" s="3">
-        <v>494100</v>
+        <v>499100</v>
       </c>
       <c r="J20" s="3">
-        <v>238300</v>
+        <v>240700</v>
       </c>
       <c r="K20" s="3">
         <v>272600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6575100</v>
+        <v>6645400</v>
       </c>
       <c r="E21" s="3">
-        <v>6584800</v>
+        <v>6654900</v>
       </c>
       <c r="F21" s="3">
-        <v>6221400</v>
+        <v>6287500</v>
       </c>
       <c r="G21" s="3">
-        <v>4870300</v>
+        <v>4922800</v>
       </c>
       <c r="H21" s="3">
-        <v>5483900</v>
+        <v>5542600</v>
       </c>
       <c r="I21" s="3">
-        <v>5463200</v>
+        <v>5521200</v>
       </c>
       <c r="J21" s="3">
-        <v>4990400</v>
+        <v>5043400</v>
       </c>
       <c r="K21" s="3">
         <v>4826500</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>526200</v>
+        <v>531500</v>
       </c>
       <c r="E22" s="3">
-        <v>399400</v>
+        <v>403400</v>
       </c>
       <c r="F22" s="3">
-        <v>444500</v>
+        <v>449000</v>
       </c>
       <c r="G22" s="3">
-        <v>403700</v>
+        <v>407800</v>
       </c>
       <c r="H22" s="3">
-        <v>392100</v>
+        <v>396000</v>
       </c>
       <c r="I22" s="3">
-        <v>356400</v>
+        <v>360000</v>
       </c>
       <c r="J22" s="3">
-        <v>350500</v>
+        <v>354100</v>
       </c>
       <c r="K22" s="3">
         <v>349000</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4728200</v>
+        <v>4775900</v>
       </c>
       <c r="E23" s="3">
-        <v>4928600</v>
+        <v>4978300</v>
       </c>
       <c r="F23" s="3">
-        <v>4615200</v>
+        <v>4661800</v>
       </c>
       <c r="G23" s="3">
-        <v>3311500</v>
+        <v>3344900</v>
       </c>
       <c r="H23" s="3">
-        <v>3956400</v>
+        <v>3996300</v>
       </c>
       <c r="I23" s="3">
-        <v>4140800</v>
+        <v>4182600</v>
       </c>
       <c r="J23" s="3">
-        <v>3708700</v>
+        <v>3746100</v>
       </c>
       <c r="K23" s="3">
         <v>3582000</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>628900</v>
+        <v>635300</v>
       </c>
       <c r="E24" s="3">
-        <v>1198800</v>
+        <v>1210900</v>
       </c>
       <c r="F24" s="3">
-        <v>1050100</v>
+        <v>1060700</v>
       </c>
       <c r="G24" s="3">
-        <v>818400</v>
+        <v>826700</v>
       </c>
       <c r="H24" s="3">
-        <v>884000</v>
+        <v>892900</v>
       </c>
       <c r="I24" s="3">
-        <v>986700</v>
+        <v>996700</v>
       </c>
       <c r="J24" s="3">
-        <v>-1573400</v>
+        <v>-1589300</v>
       </c>
       <c r="K24" s="3">
         <v>935700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4099300</v>
+        <v>4140600</v>
       </c>
       <c r="E26" s="3">
-        <v>3729800</v>
+        <v>3767400</v>
       </c>
       <c r="F26" s="3">
-        <v>3565100</v>
+        <v>3601100</v>
       </c>
       <c r="G26" s="3">
-        <v>2493100</v>
+        <v>2518200</v>
       </c>
       <c r="H26" s="3">
-        <v>3072500</v>
+        <v>3103400</v>
       </c>
       <c r="I26" s="3">
-        <v>3154100</v>
+        <v>3185900</v>
       </c>
       <c r="J26" s="3">
-        <v>5282100</v>
+        <v>5335300</v>
       </c>
       <c r="K26" s="3">
         <v>2646300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4099300</v>
+        <v>4140600</v>
       </c>
       <c r="E27" s="3">
-        <v>3729800</v>
+        <v>3767400</v>
       </c>
       <c r="F27" s="3">
-        <v>3565100</v>
+        <v>3601100</v>
       </c>
       <c r="G27" s="3">
-        <v>2493100</v>
+        <v>2518200</v>
       </c>
       <c r="H27" s="3">
-        <v>3072500</v>
+        <v>3103400</v>
       </c>
       <c r="I27" s="3">
-        <v>3154100</v>
+        <v>3185900</v>
       </c>
       <c r="J27" s="3">
-        <v>5282100</v>
+        <v>5335300</v>
       </c>
       <c r="K27" s="3">
         <v>2646300</v>
@@ -1599,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="G29" s="3">
-        <v>102800</v>
+        <v>103800</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>8</v>
@@ -1608,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="J29" s="3">
-        <v>-1285500</v>
+        <v>-1298500</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-446700</v>
+        <v>-451200</v>
       </c>
       <c r="E32" s="3">
-        <v>-343200</v>
+        <v>-346700</v>
       </c>
       <c r="F32" s="3">
-        <v>-321400</v>
+        <v>-324600</v>
       </c>
       <c r="G32" s="3">
-        <v>-233900</v>
+        <v>-236300</v>
       </c>
       <c r="H32" s="3">
-        <v>-272600</v>
+        <v>-275300</v>
       </c>
       <c r="I32" s="3">
-        <v>-494100</v>
+        <v>-499100</v>
       </c>
       <c r="J32" s="3">
-        <v>-238300</v>
+        <v>-240700</v>
       </c>
       <c r="K32" s="3">
         <v>-272600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4099300</v>
+        <v>4140600</v>
       </c>
       <c r="E33" s="3">
-        <v>3729800</v>
+        <v>3767400</v>
       </c>
       <c r="F33" s="3">
-        <v>3565100</v>
+        <v>3601100</v>
       </c>
       <c r="G33" s="3">
-        <v>2595800</v>
+        <v>2622000</v>
       </c>
       <c r="H33" s="3">
-        <v>3072500</v>
+        <v>3103400</v>
       </c>
       <c r="I33" s="3">
-        <v>3154100</v>
+        <v>3185900</v>
       </c>
       <c r="J33" s="3">
-        <v>3996500</v>
+        <v>4036800</v>
       </c>
       <c r="K33" s="3">
         <v>2646300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4099300</v>
+        <v>4140600</v>
       </c>
       <c r="E35" s="3">
-        <v>3729800</v>
+        <v>3767400</v>
       </c>
       <c r="F35" s="3">
-        <v>3565100</v>
+        <v>3601100</v>
       </c>
       <c r="G35" s="3">
-        <v>2595800</v>
+        <v>2622000</v>
       </c>
       <c r="H35" s="3">
-        <v>3072500</v>
+        <v>3103400</v>
       </c>
       <c r="I35" s="3">
-        <v>3154100</v>
+        <v>3185900</v>
       </c>
       <c r="J35" s="3">
-        <v>3996500</v>
+        <v>4036800</v>
       </c>
       <c r="K35" s="3">
         <v>2646300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>346200</v>
+        <v>349700</v>
       </c>
       <c r="E41" s="3">
-        <v>239000</v>
+        <v>241400</v>
       </c>
       <c r="F41" s="3">
-        <v>610700</v>
+        <v>616900</v>
       </c>
       <c r="G41" s="3">
-        <v>414700</v>
+        <v>418800</v>
       </c>
       <c r="H41" s="3">
-        <v>46600</v>
+        <v>47100</v>
       </c>
       <c r="I41" s="3">
-        <v>193900</v>
+        <v>195800</v>
       </c>
       <c r="J41" s="3">
-        <v>51000</v>
+        <v>51500</v>
       </c>
       <c r="K41" s="3">
         <v>128000</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>947400</v>
+        <v>956900</v>
       </c>
       <c r="E43" s="3">
-        <v>1032700</v>
+        <v>1043100</v>
       </c>
       <c r="F43" s="3">
-        <v>782700</v>
+        <v>790600</v>
       </c>
       <c r="G43" s="3">
-        <v>830100</v>
+        <v>838400</v>
       </c>
       <c r="H43" s="3">
-        <v>884000</v>
+        <v>892900</v>
       </c>
       <c r="I43" s="3">
-        <v>851900</v>
+        <v>860500</v>
       </c>
       <c r="J43" s="3">
-        <v>717100</v>
+        <v>724300</v>
       </c>
       <c r="K43" s="3">
         <v>636100</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>514500</v>
+      </c>
+      <c r="E44" s="3">
         <v>509400</v>
       </c>
-      <c r="E44" s="3">
-        <v>504300</v>
-      </c>
       <c r="F44" s="3">
+        <v>433600</v>
+      </c>
+      <c r="G44" s="3">
         <v>429200</v>
       </c>
-      <c r="G44" s="3">
-        <v>424900</v>
-      </c>
       <c r="H44" s="3">
-        <v>445300</v>
+        <v>449800</v>
       </c>
       <c r="I44" s="3">
-        <v>405900</v>
+        <v>410000</v>
       </c>
       <c r="J44" s="3">
-        <v>309000</v>
+        <v>312100</v>
       </c>
       <c r="K44" s="3">
         <v>258100</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>448200</v>
+        <v>452700</v>
       </c>
       <c r="E45" s="3">
-        <v>568400</v>
+        <v>574200</v>
       </c>
       <c r="F45" s="3">
-        <v>674100</v>
+        <v>680900</v>
       </c>
       <c r="G45" s="3">
-        <v>591000</v>
+        <v>597000</v>
       </c>
       <c r="H45" s="3">
-        <v>686500</v>
+        <v>693400</v>
       </c>
       <c r="I45" s="3">
-        <v>536400</v>
+        <v>541800</v>
       </c>
       <c r="J45" s="3">
-        <v>518900</v>
+        <v>524100</v>
       </c>
       <c r="K45" s="3">
         <v>509600</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2251100</v>
+        <v>2273800</v>
       </c>
       <c r="E46" s="3">
-        <v>2344400</v>
+        <v>2368100</v>
       </c>
       <c r="F46" s="3">
-        <v>2496700</v>
+        <v>2521900</v>
       </c>
       <c r="G46" s="3">
-        <v>2260600</v>
+        <v>2283400</v>
       </c>
       <c r="H46" s="3">
-        <v>2062400</v>
+        <v>2083200</v>
       </c>
       <c r="I46" s="3">
-        <v>1988100</v>
+        <v>2008100</v>
       </c>
       <c r="J46" s="3">
-        <v>1596000</v>
+        <v>1612100</v>
       </c>
       <c r="K46" s="3">
         <v>1531800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>304600</v>
+        <v>307700</v>
       </c>
       <c r="E47" s="3">
-        <v>86700</v>
+        <v>87600</v>
       </c>
       <c r="F47" s="3">
-        <v>110000</v>
+        <v>111200</v>
       </c>
       <c r="G47" s="3">
-        <v>87500</v>
+        <v>88300</v>
       </c>
       <c r="H47" s="3">
-        <v>83800</v>
+        <v>84700</v>
       </c>
       <c r="I47" s="3">
-        <v>70000</v>
+        <v>70700</v>
       </c>
       <c r="J47" s="3">
-        <v>72100</v>
+        <v>72900</v>
       </c>
       <c r="K47" s="3">
         <v>73400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>32824100</v>
+        <v>33155100</v>
       </c>
       <c r="E48" s="3">
-        <v>32070500</v>
+        <v>32394000</v>
       </c>
       <c r="F48" s="3">
-        <v>30333200</v>
+        <v>30639100</v>
       </c>
       <c r="G48" s="3">
-        <v>29517700</v>
+        <v>29815400</v>
       </c>
       <c r="H48" s="3">
-        <v>29288100</v>
+        <v>29583500</v>
       </c>
       <c r="I48" s="3">
-        <v>27527500</v>
+        <v>27805100</v>
       </c>
       <c r="J48" s="3">
-        <v>24915600</v>
+        <v>25166900</v>
       </c>
       <c r="K48" s="3">
         <v>24540200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>146500</v>
+        <v>148000</v>
       </c>
       <c r="E49" s="3">
-        <v>150900</v>
+        <v>152400</v>
       </c>
       <c r="F49" s="3">
-        <v>152300</v>
+        <v>153800</v>
       </c>
       <c r="G49" s="3">
-        <v>156700</v>
+        <v>158300</v>
       </c>
       <c r="H49" s="3">
-        <v>166900</v>
+        <v>168600</v>
       </c>
       <c r="I49" s="3">
-        <v>53200</v>
+        <v>53700</v>
       </c>
       <c r="J49" s="3">
-        <v>45200</v>
+        <v>45600</v>
       </c>
       <c r="K49" s="3">
         <v>48700</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2854600</v>
+        <v>2883300</v>
       </c>
       <c r="E52" s="3">
-        <v>2267900</v>
+        <v>2290800</v>
       </c>
       <c r="F52" s="3">
-        <v>2280300</v>
+        <v>2303300</v>
       </c>
       <c r="G52" s="3">
-        <v>628900</v>
+        <v>635300</v>
       </c>
       <c r="H52" s="3">
-        <v>306800</v>
+        <v>309900</v>
       </c>
       <c r="I52" s="3">
-        <v>396400</v>
+        <v>400400</v>
       </c>
       <c r="J52" s="3">
-        <v>793600</v>
+        <v>801600</v>
       </c>
       <c r="K52" s="3">
         <v>746600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>38380900</v>
+        <v>38768000</v>
       </c>
       <c r="E54" s="3">
-        <v>36920400</v>
+        <v>37292800</v>
       </c>
       <c r="F54" s="3">
-        <v>35372600</v>
+        <v>35729300</v>
       </c>
       <c r="G54" s="3">
-        <v>32651400</v>
+        <v>32980700</v>
       </c>
       <c r="H54" s="3">
-        <v>31908000</v>
+        <v>32229800</v>
       </c>
       <c r="I54" s="3">
-        <v>30035100</v>
+        <v>30338000</v>
       </c>
       <c r="J54" s="3">
-        <v>27422500</v>
+        <v>27699100</v>
       </c>
       <c r="K54" s="3">
         <v>26940800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>705400</v>
+        <v>712600</v>
       </c>
       <c r="E57" s="3">
-        <v>695200</v>
+        <v>702200</v>
       </c>
       <c r="F57" s="3">
-        <v>658100</v>
+        <v>664700</v>
       </c>
       <c r="G57" s="3">
-        <v>568400</v>
+        <v>574200</v>
       </c>
       <c r="H57" s="3">
-        <v>631100</v>
+        <v>637500</v>
       </c>
       <c r="I57" s="3">
-        <v>715600</v>
+        <v>722900</v>
       </c>
       <c r="J57" s="3">
-        <v>1373000</v>
+        <v>1386800</v>
       </c>
       <c r="K57" s="3">
         <v>1103600</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1705300</v>
+        <v>1722500</v>
       </c>
       <c r="E58" s="3">
-        <v>770300</v>
+        <v>778100</v>
       </c>
       <c r="F58" s="3">
-        <v>370200</v>
+        <v>373900</v>
       </c>
       <c r="G58" s="3">
-        <v>663200</v>
+        <v>669900</v>
       </c>
       <c r="H58" s="3">
-        <v>1406500</v>
+        <v>1420700</v>
       </c>
       <c r="I58" s="3">
-        <v>862900</v>
+        <v>871600</v>
       </c>
       <c r="J58" s="3">
-        <v>1515800</v>
+        <v>1531100</v>
       </c>
       <c r="K58" s="3">
         <v>1082500</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1258600</v>
+        <v>1271300</v>
       </c>
       <c r="E59" s="3">
-        <v>1334400</v>
+        <v>1347800</v>
       </c>
       <c r="F59" s="3">
-        <v>1245500</v>
+        <v>1258000</v>
       </c>
       <c r="G59" s="3">
-        <v>1154400</v>
+        <v>1166000</v>
       </c>
       <c r="H59" s="3">
-        <v>1086600</v>
+        <v>1097500</v>
       </c>
       <c r="I59" s="3">
-        <v>972200</v>
+        <v>982000</v>
       </c>
       <c r="J59" s="3">
-        <v>13800</v>
+        <v>14000</v>
       </c>
       <c r="K59" s="3">
         <v>700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3669300</v>
+        <v>3706300</v>
       </c>
       <c r="E60" s="3">
-        <v>2799900</v>
+        <v>2828100</v>
       </c>
       <c r="F60" s="3">
-        <v>2273700</v>
+        <v>2296700</v>
       </c>
       <c r="G60" s="3">
-        <v>2386000</v>
+        <v>2410000</v>
       </c>
       <c r="H60" s="3">
-        <v>3124200</v>
+        <v>3155700</v>
       </c>
       <c r="I60" s="3">
-        <v>2550700</v>
+        <v>2576400</v>
       </c>
       <c r="J60" s="3">
-        <v>2902700</v>
+        <v>2931900</v>
       </c>
       <c r="K60" s="3">
         <v>2186800</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11757100</v>
+        <v>11875700</v>
       </c>
       <c r="E61" s="3">
-        <v>10473700</v>
+        <v>10579400</v>
       </c>
       <c r="F61" s="3">
-        <v>8728400</v>
+        <v>8816400</v>
       </c>
       <c r="G61" s="3">
-        <v>8742200</v>
+        <v>8830400</v>
       </c>
       <c r="H61" s="3">
-        <v>8647500</v>
+        <v>8734700</v>
       </c>
       <c r="I61" s="3">
-        <v>8296900</v>
+        <v>8380600</v>
       </c>
       <c r="J61" s="3">
-        <v>6375200</v>
+        <v>6439500</v>
       </c>
       <c r="K61" s="3">
         <v>6868800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8294000</v>
+        <v>8377700</v>
       </c>
       <c r="E62" s="3">
-        <v>8063000</v>
+        <v>8144300</v>
       </c>
       <c r="F62" s="3">
-        <v>7795500</v>
+        <v>7874200</v>
       </c>
       <c r="G62" s="3">
-        <v>7202300</v>
+        <v>7275000</v>
       </c>
       <c r="H62" s="3">
-        <v>6988800</v>
+        <v>7059300</v>
       </c>
       <c r="I62" s="3">
-        <v>6331500</v>
+        <v>6395300</v>
       </c>
       <c r="J62" s="3">
-        <v>6006400</v>
+        <v>6067000</v>
       </c>
       <c r="K62" s="3">
         <v>7095600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23720400</v>
+        <v>23959600</v>
       </c>
       <c r="E66" s="3">
-        <v>21336600</v>
+        <v>21551800</v>
       </c>
       <c r="F66" s="3">
-        <v>18797600</v>
+        <v>18987200</v>
       </c>
       <c r="G66" s="3">
-        <v>18330500</v>
+        <v>18515400</v>
       </c>
       <c r="H66" s="3">
-        <v>18760500</v>
+        <v>18949700</v>
       </c>
       <c r="I66" s="3">
-        <v>17179100</v>
+        <v>17352300</v>
       </c>
       <c r="J66" s="3">
-        <v>15284300</v>
+        <v>15438400</v>
       </c>
       <c r="K66" s="3">
         <v>16151300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>13595000</v>
+        <v>13732100</v>
       </c>
       <c r="E72" s="3">
-        <v>14232000</v>
+        <v>14375500</v>
       </c>
       <c r="F72" s="3">
-        <v>15115200</v>
+        <v>15267700</v>
       </c>
       <c r="G72" s="3">
-        <v>13963800</v>
+        <v>14104600</v>
       </c>
       <c r="H72" s="3">
-        <v>12851000</v>
+        <v>12980600</v>
       </c>
       <c r="I72" s="3">
-        <v>12114200</v>
+        <v>12236400</v>
       </c>
       <c r="J72" s="3">
-        <v>11358500</v>
+        <v>11473000</v>
       </c>
       <c r="K72" s="3">
         <v>9627100</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14660500</v>
+        <v>14808300</v>
       </c>
       <c r="E76" s="3">
-        <v>15583800</v>
+        <v>15741000</v>
       </c>
       <c r="F76" s="3">
-        <v>16574900</v>
+        <v>16742100</v>
       </c>
       <c r="G76" s="3">
-        <v>14320900</v>
+        <v>14465300</v>
       </c>
       <c r="H76" s="3">
-        <v>13147600</v>
+        <v>13280200</v>
       </c>
       <c r="I76" s="3">
-        <v>12856100</v>
+        <v>12985700</v>
       </c>
       <c r="J76" s="3">
-        <v>12138200</v>
+        <v>12260600</v>
       </c>
       <c r="K76" s="3">
         <v>10789600</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4099300</v>
+        <v>4140600</v>
       </c>
       <c r="E81" s="3">
-        <v>3729800</v>
+        <v>3767400</v>
       </c>
       <c r="F81" s="3">
-        <v>3565100</v>
+        <v>3601100</v>
       </c>
       <c r="G81" s="3">
-        <v>2595800</v>
+        <v>2622000</v>
       </c>
       <c r="H81" s="3">
-        <v>3072500</v>
+        <v>3103400</v>
       </c>
       <c r="I81" s="3">
-        <v>3154100</v>
+        <v>3185900</v>
       </c>
       <c r="J81" s="3">
-        <v>3996500</v>
+        <v>4036800</v>
       </c>
       <c r="K81" s="3">
         <v>2646300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1324200</v>
+        <v>1337500</v>
       </c>
       <c r="E83" s="3">
-        <v>1260000</v>
+        <v>1272700</v>
       </c>
       <c r="F83" s="3">
-        <v>1164600</v>
+        <v>1176300</v>
       </c>
       <c r="G83" s="3">
-        <v>1158000</v>
+        <v>1169700</v>
       </c>
       <c r="H83" s="3">
-        <v>1138300</v>
+        <v>1149800</v>
       </c>
       <c r="I83" s="3">
-        <v>968500</v>
+        <v>978300</v>
       </c>
       <c r="J83" s="3">
-        <v>933500</v>
+        <v>943000</v>
       </c>
       <c r="K83" s="3">
         <v>890600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5075800</v>
+        <v>5127000</v>
       </c>
       <c r="E89" s="3">
-        <v>4858600</v>
+        <v>4907600</v>
       </c>
       <c r="F89" s="3">
-        <v>5080200</v>
+        <v>5131400</v>
       </c>
       <c r="G89" s="3">
-        <v>4492800</v>
+        <v>4538100</v>
       </c>
       <c r="H89" s="3">
-        <v>4316400</v>
+        <v>4360000</v>
       </c>
       <c r="I89" s="3">
-        <v>4312800</v>
+        <v>4356300</v>
       </c>
       <c r="J89" s="3">
-        <v>4019800</v>
+        <v>4060400</v>
       </c>
       <c r="K89" s="3">
         <v>3781900</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2322600</v>
+        <v>-2346000</v>
       </c>
       <c r="E91" s="3">
-        <v>-2004100</v>
+        <v>-2024300</v>
       </c>
       <c r="F91" s="3">
-        <v>-2106800</v>
+        <v>-2128100</v>
       </c>
       <c r="G91" s="3">
-        <v>-2086400</v>
+        <v>-2107500</v>
       </c>
       <c r="H91" s="3">
-        <v>-2816700</v>
+        <v>-2845100</v>
       </c>
       <c r="I91" s="3">
-        <v>-2573300</v>
+        <v>-2599200</v>
       </c>
       <c r="J91" s="3">
-        <v>-1948000</v>
+        <v>-1967600</v>
       </c>
       <c r="K91" s="3">
         <v>-1959300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2527300</v>
+        <v>-2552800</v>
       </c>
       <c r="E94" s="3">
-        <v>-1829200</v>
+        <v>-1847600</v>
       </c>
       <c r="F94" s="3">
-        <v>-2093700</v>
+        <v>-2114800</v>
       </c>
       <c r="G94" s="3">
-        <v>-2146900</v>
+        <v>-2168600</v>
       </c>
       <c r="H94" s="3">
-        <v>-3053500</v>
+        <v>-3084300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2480700</v>
+        <v>-2505700</v>
       </c>
       <c r="J94" s="3">
-        <v>-1995300</v>
+        <v>-2015500</v>
       </c>
       <c r="K94" s="3">
         <v>-1949800</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1509300</v>
+        <v>-1524500</v>
       </c>
       <c r="E96" s="3">
-        <v>-1460400</v>
+        <v>-1475200</v>
       </c>
       <c r="F96" s="3">
-        <v>-1268000</v>
+        <v>-1280800</v>
       </c>
       <c r="G96" s="3">
-        <v>-1190800</v>
+        <v>-1202800</v>
       </c>
       <c r="H96" s="3">
-        <v>-1125200</v>
+        <v>-1136600</v>
       </c>
       <c r="I96" s="3">
-        <v>-971400</v>
+        <v>-981200</v>
       </c>
       <c r="J96" s="3">
-        <v>-902900</v>
+        <v>-912000</v>
       </c>
       <c r="K96" s="3">
         <v>-842600</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2482200</v>
+        <v>-2507200</v>
       </c>
       <c r="E100" s="3">
-        <v>-3401100</v>
+        <v>-3435400</v>
       </c>
       <c r="F100" s="3">
-        <v>-2810800</v>
+        <v>-2839200</v>
       </c>
       <c r="G100" s="3">
-        <v>-1972800</v>
+        <v>-1992600</v>
       </c>
       <c r="H100" s="3">
-        <v>-1386800</v>
+        <v>-1400800</v>
       </c>
       <c r="I100" s="3">
-        <v>-1682000</v>
+        <v>-1698900</v>
       </c>
       <c r="J100" s="3">
-        <v>-2109800</v>
+        <v>-2131000</v>
       </c>
       <c r="K100" s="3">
         <v>-1845900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>65600</v>
+        <v>66200</v>
       </c>
       <c r="E102" s="3">
-        <v>-369500</v>
+        <v>-373200</v>
       </c>
       <c r="F102" s="3">
-        <v>175600</v>
+        <v>177400</v>
       </c>
       <c r="G102" s="3">
-        <v>373100</v>
+        <v>376900</v>
       </c>
       <c r="H102" s="3">
-        <v>-124600</v>
+        <v>-125900</v>
       </c>
       <c r="I102" s="3">
-        <v>150100</v>
+        <v>151600</v>
       </c>
       <c r="J102" s="3">
-        <v>-86700</v>
+        <v>-87600</v>
       </c>
       <c r="K102" s="3">
         <v>-2900</v>

--- a/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>CNI</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>12387300</v>
+        <v>12742400</v>
       </c>
       <c r="E8" s="3">
-        <v>12592600</v>
+        <v>12639800</v>
       </c>
       <c r="F8" s="3">
-        <v>10656700</v>
+        <v>11439800</v>
       </c>
       <c r="G8" s="3">
-        <v>10172300</v>
+        <v>10845200</v>
       </c>
       <c r="H8" s="3">
-        <v>10980600</v>
+        <v>11500800</v>
       </c>
       <c r="I8" s="3">
-        <v>10541800</v>
+        <v>10495100</v>
       </c>
       <c r="J8" s="3">
-        <v>9599600</v>
+        <v>10398900</v>
       </c>
       <c r="K8" s="3">
         <v>8751000</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3202800</v>
+        <v>5589000</v>
       </c>
       <c r="E9" s="3">
-        <v>3466300</v>
+        <v>5529700</v>
       </c>
       <c r="F9" s="3">
-        <v>2646300</v>
+        <v>5028900</v>
       </c>
       <c r="G9" s="3">
-        <v>2432100</v>
+        <v>4839900</v>
       </c>
       <c r="H9" s="3">
-        <v>2873800</v>
+        <v>5333700</v>
       </c>
       <c r="I9" s="3">
-        <v>2725800</v>
+        <v>4930600</v>
       </c>
       <c r="J9" s="3">
-        <v>2304800</v>
+        <v>4601000</v>
       </c>
       <c r="K9" s="3">
         <v>1921500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9184400</v>
+        <v>7153400</v>
       </c>
       <c r="E10" s="3">
-        <v>9126300</v>
+        <v>7110100</v>
       </c>
       <c r="F10" s="3">
-        <v>8010300</v>
+        <v>6411000</v>
       </c>
       <c r="G10" s="3">
-        <v>7740200</v>
+        <v>6005300</v>
       </c>
       <c r="H10" s="3">
-        <v>8106800</v>
+        <v>6167100</v>
       </c>
       <c r="I10" s="3">
-        <v>7816000</v>
+        <v>5564500</v>
       </c>
       <c r="J10" s="3">
-        <v>7294900</v>
+        <v>5797900</v>
       </c>
       <c r="K10" s="3">
         <v>6829500</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-103000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>10300</v>
       </c>
       <c r="F14" s="3">
-        <v>-590400</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+        <v>-745200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>771500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>364700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-260200</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-17500</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1337500</v>
+        <v>1375900</v>
       </c>
       <c r="E15" s="3">
-        <v>1272700</v>
+        <v>1277500</v>
       </c>
       <c r="F15" s="3">
-        <v>1176300</v>
+        <v>1262800</v>
       </c>
       <c r="G15" s="3">
-        <v>1169700</v>
+        <v>1247100</v>
       </c>
       <c r="H15" s="3">
-        <v>1149800</v>
+        <v>1204300</v>
       </c>
       <c r="I15" s="3">
-        <v>978300</v>
+        <v>974000</v>
       </c>
       <c r="J15" s="3">
-        <v>943000</v>
+        <v>1021500</v>
       </c>
       <c r="K15" s="3">
         <v>890600</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7531100</v>
+        <v>7384400</v>
       </c>
       <c r="E17" s="3">
-        <v>7557600</v>
+        <v>7218000</v>
       </c>
       <c r="F17" s="3">
-        <v>5870500</v>
+        <v>6691500</v>
       </c>
       <c r="G17" s="3">
-        <v>6655900</v>
+        <v>6087000</v>
       </c>
       <c r="H17" s="3">
-        <v>6863500</v>
+        <v>6538000</v>
       </c>
       <c r="I17" s="3">
-        <v>6498400</v>
+        <v>6248300</v>
       </c>
       <c r="J17" s="3">
-        <v>5740200</v>
+        <v>5966900</v>
       </c>
       <c r="K17" s="3">
         <v>5092700</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4856100</v>
+        <v>5358000</v>
       </c>
       <c r="E18" s="3">
-        <v>5035000</v>
+        <v>5421800</v>
       </c>
       <c r="F18" s="3">
-        <v>4786200</v>
+        <v>4748400</v>
       </c>
       <c r="G18" s="3">
-        <v>3516400</v>
+        <v>4758300</v>
       </c>
       <c r="H18" s="3">
-        <v>4117100</v>
+        <v>4962900</v>
       </c>
       <c r="I18" s="3">
-        <v>4043500</v>
+        <v>4246900</v>
       </c>
       <c r="J18" s="3">
-        <v>3859400</v>
+        <v>4431900</v>
       </c>
       <c r="K18" s="3">
         <v>3658300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>451200</v>
+        <v>1500</v>
       </c>
       <c r="E20" s="3">
-        <v>346700</v>
+        <v>9600</v>
       </c>
       <c r="F20" s="3">
-        <v>324600</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>236300</v>
+        <v>3900</v>
       </c>
       <c r="H20" s="3">
-        <v>275300</v>
+        <v>-2300</v>
       </c>
       <c r="I20" s="3">
-        <v>499100</v>
+        <v>-15400</v>
       </c>
       <c r="J20" s="3">
-        <v>240700</v>
+        <v>8000</v>
       </c>
       <c r="K20" s="3">
         <v>272600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6645400</v>
+        <v>6732400</v>
       </c>
       <c r="E21" s="3">
-        <v>6654900</v>
+        <v>6689700</v>
       </c>
       <c r="F21" s="3">
-        <v>6287500</v>
+        <v>6011100</v>
       </c>
       <c r="G21" s="3">
-        <v>4922800</v>
+        <v>6001400</v>
       </c>
       <c r="H21" s="3">
-        <v>5542600</v>
+        <v>6169500</v>
       </c>
       <c r="I21" s="3">
-        <v>5521200</v>
+        <v>5236200</v>
       </c>
       <c r="J21" s="3">
-        <v>5043400</v>
+        <v>5445400</v>
       </c>
       <c r="K21" s="3">
         <v>4826500</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>531500</v>
+        <v>546700</v>
       </c>
       <c r="E22" s="3">
-        <v>403400</v>
+        <v>404900</v>
       </c>
       <c r="F22" s="3">
-        <v>449000</v>
+        <v>482000</v>
       </c>
       <c r="G22" s="3">
-        <v>407800</v>
+        <v>434800</v>
       </c>
       <c r="H22" s="3">
-        <v>396000</v>
+        <v>414800</v>
       </c>
       <c r="I22" s="3">
-        <v>360000</v>
+        <v>358400</v>
       </c>
       <c r="J22" s="3">
-        <v>354100</v>
+        <v>383500</v>
       </c>
       <c r="K22" s="3">
         <v>349000</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4775900</v>
+        <v>4912800</v>
       </c>
       <c r="E23" s="3">
-        <v>4978300</v>
+        <v>4997000</v>
       </c>
       <c r="F23" s="3">
-        <v>4661800</v>
+        <v>5011500</v>
       </c>
       <c r="G23" s="3">
-        <v>3344900</v>
+        <v>3548100</v>
       </c>
       <c r="H23" s="3">
-        <v>3996300</v>
+        <v>4185700</v>
       </c>
       <c r="I23" s="3">
-        <v>4182600</v>
+        <v>4164000</v>
       </c>
       <c r="J23" s="3">
-        <v>3746100</v>
+        <v>4058000</v>
       </c>
       <c r="K23" s="3">
         <v>3582000</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>635300</v>
+        <v>653500</v>
       </c>
       <c r="E24" s="3">
-        <v>1210900</v>
+        <v>1215400</v>
       </c>
       <c r="F24" s="3">
-        <v>1060700</v>
+        <v>1140300</v>
       </c>
       <c r="G24" s="3">
-        <v>826700</v>
+        <v>766000</v>
       </c>
       <c r="H24" s="3">
-        <v>892900</v>
+        <v>935200</v>
       </c>
       <c r="I24" s="3">
-        <v>996700</v>
+        <v>992300</v>
       </c>
       <c r="J24" s="3">
-        <v>-1589300</v>
+        <v>-315000</v>
       </c>
       <c r="K24" s="3">
         <v>935700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4140600</v>
+        <v>4259300</v>
       </c>
       <c r="E26" s="3">
-        <v>3767400</v>
+        <v>3781500</v>
       </c>
       <c r="F26" s="3">
-        <v>3601100</v>
+        <v>3871200</v>
       </c>
       <c r="G26" s="3">
-        <v>2518200</v>
+        <v>2782100</v>
       </c>
       <c r="H26" s="3">
-        <v>3103400</v>
+        <v>3250500</v>
       </c>
       <c r="I26" s="3">
-        <v>3185900</v>
+        <v>3171800</v>
       </c>
       <c r="J26" s="3">
-        <v>5335300</v>
+        <v>4372900</v>
       </c>
       <c r="K26" s="3">
         <v>2646300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4140600</v>
+        <v>4259300</v>
       </c>
       <c r="E27" s="3">
-        <v>3767400</v>
+        <v>3781500</v>
       </c>
       <c r="F27" s="3">
-        <v>3601100</v>
+        <v>3871200</v>
       </c>
       <c r="G27" s="3">
-        <v>2518200</v>
+        <v>2782100</v>
       </c>
       <c r="H27" s="3">
-        <v>3103400</v>
+        <v>3250500</v>
       </c>
       <c r="I27" s="3">
-        <v>3185900</v>
+        <v>3171800</v>
       </c>
       <c r="J27" s="3">
-        <v>5335300</v>
+        <v>4372900</v>
       </c>
       <c r="K27" s="3">
         <v>2646300</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>103800</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-1298500</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-451200</v>
+        <v>-1500</v>
       </c>
       <c r="E32" s="3">
-        <v>-346700</v>
+        <v>-9600</v>
       </c>
       <c r="F32" s="3">
-        <v>-324600</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-236300</v>
+        <v>-3900</v>
       </c>
       <c r="H32" s="3">
-        <v>-275300</v>
+        <v>2300</v>
       </c>
       <c r="I32" s="3">
-        <v>-499100</v>
+        <v>15400</v>
       </c>
       <c r="J32" s="3">
-        <v>-240700</v>
+        <v>-8000</v>
       </c>
       <c r="K32" s="3">
         <v>-272600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4140600</v>
+        <v>4259300</v>
       </c>
       <c r="E33" s="3">
-        <v>3767400</v>
+        <v>3781500</v>
       </c>
       <c r="F33" s="3">
-        <v>3601100</v>
+        <v>3871200</v>
       </c>
       <c r="G33" s="3">
-        <v>2622000</v>
+        <v>2782100</v>
       </c>
       <c r="H33" s="3">
-        <v>3103400</v>
+        <v>3250500</v>
       </c>
       <c r="I33" s="3">
-        <v>3185900</v>
+        <v>3171800</v>
       </c>
       <c r="J33" s="3">
-        <v>4036800</v>
+        <v>4372900</v>
       </c>
       <c r="K33" s="3">
         <v>2646300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4140600</v>
+        <v>4259300</v>
       </c>
       <c r="E35" s="3">
-        <v>3767400</v>
+        <v>3781500</v>
       </c>
       <c r="F35" s="3">
-        <v>3601100</v>
+        <v>3871200</v>
       </c>
       <c r="G35" s="3">
-        <v>2622000</v>
+        <v>2782100</v>
       </c>
       <c r="H35" s="3">
-        <v>3103400</v>
+        <v>3250500</v>
       </c>
       <c r="I35" s="3">
-        <v>3185900</v>
+        <v>3171800</v>
       </c>
       <c r="J35" s="3">
-        <v>4036800</v>
+        <v>4372900</v>
       </c>
       <c r="K35" s="3">
         <v>2646300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>349700</v>
+        <v>359700</v>
       </c>
       <c r="E41" s="3">
-        <v>241400</v>
+        <v>242300</v>
       </c>
       <c r="F41" s="3">
-        <v>616900</v>
+        <v>662200</v>
       </c>
       <c r="G41" s="3">
-        <v>418800</v>
+        <v>446600</v>
       </c>
       <c r="H41" s="3">
-        <v>47100</v>
+        <v>49300</v>
       </c>
       <c r="I41" s="3">
-        <v>195800</v>
+        <v>194900</v>
       </c>
       <c r="J41" s="3">
-        <v>51500</v>
+        <v>55800</v>
       </c>
       <c r="K41" s="3">
         <v>128000</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>956900</v>
+        <v>984400</v>
       </c>
       <c r="E43" s="3">
-        <v>1043100</v>
+        <v>1047000</v>
       </c>
       <c r="F43" s="3">
-        <v>790600</v>
+        <v>848700</v>
       </c>
       <c r="G43" s="3">
-        <v>838400</v>
+        <v>893900</v>
       </c>
       <c r="H43" s="3">
-        <v>892900</v>
+        <v>1104100</v>
       </c>
       <c r="I43" s="3">
-        <v>860500</v>
+        <v>856700</v>
       </c>
       <c r="J43" s="3">
-        <v>724300</v>
+        <v>784600</v>
       </c>
       <c r="K43" s="3">
         <v>636100</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>514500</v>
+        <v>529300</v>
       </c>
       <c r="E44" s="3">
-        <v>509400</v>
+        <v>511300</v>
       </c>
       <c r="F44" s="3">
-        <v>433600</v>
+        <v>465400</v>
       </c>
       <c r="G44" s="3">
-        <v>429200</v>
+        <v>457500</v>
       </c>
       <c r="H44" s="3">
-        <v>449800</v>
+        <v>471100</v>
       </c>
       <c r="I44" s="3">
-        <v>410000</v>
+        <v>408200</v>
       </c>
       <c r="J44" s="3">
-        <v>312100</v>
+        <v>338100</v>
       </c>
       <c r="K44" s="3">
         <v>258100</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>452700</v>
+        <v>25000</v>
       </c>
       <c r="E45" s="3">
-        <v>574200</v>
+        <v>65000</v>
       </c>
       <c r="F45" s="3">
-        <v>680900</v>
+        <v>221300</v>
       </c>
       <c r="G45" s="3">
-        <v>597000</v>
+        <v>103600</v>
       </c>
       <c r="H45" s="3">
-        <v>693400</v>
+        <v>43900</v>
       </c>
       <c r="I45" s="3">
-        <v>541800</v>
+        <v>178100</v>
       </c>
       <c r="J45" s="3">
-        <v>524100</v>
+        <v>182600</v>
       </c>
       <c r="K45" s="3">
         <v>509600</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2273800</v>
+        <v>2339000</v>
       </c>
       <c r="E46" s="3">
-        <v>2368100</v>
+        <v>2376900</v>
       </c>
       <c r="F46" s="3">
-        <v>2521900</v>
+        <v>2707300</v>
       </c>
       <c r="G46" s="3">
-        <v>2283400</v>
+        <v>2434500</v>
       </c>
       <c r="H46" s="3">
-        <v>2083200</v>
+        <v>2181900</v>
       </c>
       <c r="I46" s="3">
-        <v>2008100</v>
+        <v>1999200</v>
       </c>
       <c r="J46" s="3">
-        <v>1612100</v>
+        <v>1746300</v>
       </c>
       <c r="K46" s="3">
         <v>1531800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>307700</v>
+        <v>304400</v>
       </c>
       <c r="E47" s="3">
-        <v>87600</v>
+        <v>69500</v>
       </c>
       <c r="F47" s="3">
-        <v>111200</v>
+        <v>94000</v>
       </c>
       <c r="G47" s="3">
-        <v>88300</v>
+        <v>65100</v>
       </c>
       <c r="H47" s="3">
-        <v>84700</v>
+        <v>64800</v>
       </c>
       <c r="I47" s="3">
-        <v>70700</v>
+        <v>51300</v>
       </c>
       <c r="J47" s="3">
-        <v>72900</v>
+        <v>58200</v>
       </c>
       <c r="K47" s="3">
         <v>73400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>33155100</v>
+        <v>32933500</v>
       </c>
       <c r="E48" s="3">
-        <v>32394000</v>
+        <v>31396800</v>
       </c>
       <c r="F48" s="3">
-        <v>30639100</v>
+        <v>31742600</v>
       </c>
       <c r="G48" s="3">
-        <v>29815400</v>
+        <v>30700800</v>
       </c>
       <c r="H48" s="3">
-        <v>29583500</v>
+        <v>29995300</v>
       </c>
       <c r="I48" s="3">
-        <v>27805100</v>
+        <v>26869100</v>
       </c>
       <c r="J48" s="3">
-        <v>25166900</v>
+        <v>26653000</v>
       </c>
       <c r="K48" s="3">
         <v>24540200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>148000</v>
+        <v>1324400</v>
       </c>
       <c r="E49" s="3">
-        <v>152400</v>
+        <v>1271600</v>
       </c>
       <c r="F49" s="3">
-        <v>153800</v>
+        <v>1313300</v>
       </c>
       <c r="G49" s="3">
-        <v>158300</v>
+        <v>1255700</v>
       </c>
       <c r="H49" s="3">
-        <v>168600</v>
+        <v>1166500</v>
       </c>
       <c r="I49" s="3">
-        <v>53700</v>
+        <v>866200</v>
       </c>
       <c r="J49" s="3">
-        <v>45600</v>
+        <v>658700</v>
       </c>
       <c r="K49" s="3">
         <v>48700</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2883300</v>
+        <v>2398900</v>
       </c>
       <c r="E52" s="3">
-        <v>2290800</v>
+        <v>2269100</v>
       </c>
       <c r="F52" s="3">
-        <v>2303300</v>
+        <v>2451200</v>
       </c>
       <c r="G52" s="3">
-        <v>635300</v>
+        <v>656100</v>
       </c>
       <c r="H52" s="3">
-        <v>309900</v>
+        <v>296800</v>
       </c>
       <c r="I52" s="3">
-        <v>400400</v>
+        <v>373000</v>
       </c>
       <c r="J52" s="3">
-        <v>801600</v>
+        <v>840500</v>
       </c>
       <c r="K52" s="3">
         <v>746600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>38768000</v>
+        <v>39879500</v>
       </c>
       <c r="E54" s="3">
-        <v>37292800</v>
+        <v>37432600</v>
       </c>
       <c r="F54" s="3">
-        <v>35729300</v>
+        <v>38355100</v>
       </c>
       <c r="G54" s="3">
-        <v>32980700</v>
+        <v>35162500</v>
       </c>
       <c r="H54" s="3">
-        <v>32229800</v>
+        <v>33757000</v>
       </c>
       <c r="I54" s="3">
-        <v>30338000</v>
+        <v>30203600</v>
       </c>
       <c r="J54" s="3">
-        <v>27699100</v>
+        <v>30005300</v>
       </c>
       <c r="K54" s="3">
         <v>26940800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>712600</v>
+        <v>733000</v>
       </c>
       <c r="E57" s="3">
-        <v>702200</v>
+        <v>704900</v>
       </c>
       <c r="F57" s="3">
-        <v>664700</v>
+        <v>713600</v>
       </c>
       <c r="G57" s="3">
-        <v>574200</v>
+        <v>612100</v>
       </c>
       <c r="H57" s="3">
-        <v>637500</v>
+        <v>667700</v>
       </c>
       <c r="I57" s="3">
-        <v>722900</v>
+        <v>719700</v>
       </c>
       <c r="J57" s="3">
-        <v>1386800</v>
+        <v>588500</v>
       </c>
       <c r="K57" s="3">
         <v>1103600</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1722500</v>
+        <v>1860500</v>
       </c>
       <c r="E58" s="3">
-        <v>778100</v>
+        <v>873300</v>
       </c>
       <c r="F58" s="3">
-        <v>373900</v>
+        <v>486800</v>
       </c>
       <c r="G58" s="3">
-        <v>669900</v>
+        <v>798100</v>
       </c>
       <c r="H58" s="3">
-        <v>1420700</v>
+        <v>1582100</v>
       </c>
       <c r="I58" s="3">
-        <v>871600</v>
+        <v>867700</v>
       </c>
       <c r="J58" s="3">
-        <v>1531100</v>
+        <v>1658600</v>
       </c>
       <c r="K58" s="3">
         <v>1082500</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1271300</v>
+        <v>456600</v>
       </c>
       <c r="E59" s="3">
-        <v>1347800</v>
+        <v>463300</v>
       </c>
       <c r="F59" s="3">
-        <v>1258000</v>
+        <v>511300</v>
       </c>
       <c r="G59" s="3">
-        <v>1166000</v>
+        <v>481100</v>
       </c>
       <c r="H59" s="3">
-        <v>1097500</v>
+        <v>426400</v>
       </c>
       <c r="I59" s="3">
-        <v>982000</v>
+        <v>343000</v>
       </c>
       <c r="J59" s="3">
-        <v>14000</v>
+        <v>345300</v>
       </c>
       <c r="K59" s="3">
         <v>700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3706300</v>
+        <v>3812600</v>
       </c>
       <c r="E60" s="3">
-        <v>2828100</v>
+        <v>2838700</v>
       </c>
       <c r="F60" s="3">
-        <v>2296700</v>
+        <v>2465400</v>
       </c>
       <c r="G60" s="3">
-        <v>2410000</v>
+        <v>2569500</v>
       </c>
       <c r="H60" s="3">
-        <v>3155700</v>
+        <v>3305200</v>
       </c>
       <c r="I60" s="3">
-        <v>2576400</v>
+        <v>2565000</v>
       </c>
       <c r="J60" s="3">
-        <v>2931900</v>
+        <v>3176000</v>
       </c>
       <c r="K60" s="3">
         <v>2186800</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11875700</v>
+        <v>12441800</v>
       </c>
       <c r="E61" s="3">
-        <v>10579400</v>
+        <v>10871000</v>
       </c>
       <c r="F61" s="3">
-        <v>8816400</v>
+        <v>9718800</v>
       </c>
       <c r="G61" s="3">
-        <v>8830400</v>
+        <v>9658600</v>
       </c>
       <c r="H61" s="3">
-        <v>8734700</v>
+        <v>9440800</v>
       </c>
       <c r="I61" s="3">
-        <v>8380600</v>
+        <v>8343500</v>
       </c>
       <c r="J61" s="3">
-        <v>6439500</v>
+        <v>6975600</v>
       </c>
       <c r="K61" s="3">
         <v>6868800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8377700</v>
+        <v>333200</v>
       </c>
       <c r="E62" s="3">
-        <v>8144300</v>
+        <v>314000</v>
       </c>
       <c r="F62" s="3">
-        <v>7874200</v>
+        <v>337400</v>
       </c>
       <c r="G62" s="3">
-        <v>7275000</v>
+        <v>352400</v>
       </c>
       <c r="H62" s="3">
-        <v>7059300</v>
+        <v>364700</v>
       </c>
       <c r="I62" s="3">
-        <v>6395300</v>
+        <v>367200</v>
       </c>
       <c r="J62" s="3">
-        <v>6067000</v>
+        <v>470500</v>
       </c>
       <c r="K62" s="3">
         <v>7095600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23959600</v>
+        <v>24646600</v>
       </c>
       <c r="E66" s="3">
-        <v>21551800</v>
+        <v>21632600</v>
       </c>
       <c r="F66" s="3">
-        <v>18987200</v>
+        <v>20382600</v>
       </c>
       <c r="G66" s="3">
-        <v>18515400</v>
+        <v>19740200</v>
       </c>
       <c r="H66" s="3">
-        <v>18949700</v>
+        <v>19847600</v>
       </c>
       <c r="I66" s="3">
-        <v>17352300</v>
+        <v>17275400</v>
       </c>
       <c r="J66" s="3">
-        <v>15438400</v>
+        <v>16723800</v>
       </c>
       <c r="K66" s="3">
         <v>16151300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>13732100</v>
+        <v>14125800</v>
       </c>
       <c r="E72" s="3">
-        <v>14375500</v>
+        <v>14429400</v>
       </c>
       <c r="F72" s="3">
-        <v>15267700</v>
+        <v>16584100</v>
       </c>
       <c r="G72" s="3">
-        <v>14104600</v>
+        <v>15037700</v>
       </c>
       <c r="H72" s="3">
-        <v>12980600</v>
+        <v>13595600</v>
       </c>
       <c r="I72" s="3">
-        <v>12236400</v>
+        <v>12182100</v>
       </c>
       <c r="J72" s="3">
-        <v>11473000</v>
+        <v>12408300</v>
       </c>
       <c r="K72" s="3">
         <v>9627100</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14808300</v>
+        <v>15232900</v>
       </c>
       <c r="E76" s="3">
-        <v>15741000</v>
+        <v>15800000</v>
       </c>
       <c r="F76" s="3">
-        <v>16742100</v>
+        <v>17972500</v>
       </c>
       <c r="G76" s="3">
-        <v>14465300</v>
+        <v>15422200</v>
       </c>
       <c r="H76" s="3">
-        <v>13280200</v>
+        <v>13909400</v>
       </c>
       <c r="I76" s="3">
-        <v>12985700</v>
+        <v>12928200</v>
       </c>
       <c r="J76" s="3">
-        <v>12260600</v>
+        <v>13281400</v>
       </c>
       <c r="K76" s="3">
         <v>10789600</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4140600</v>
+        <v>4259300</v>
       </c>
       <c r="E81" s="3">
-        <v>3767400</v>
+        <v>3781500</v>
       </c>
       <c r="F81" s="3">
-        <v>3601100</v>
+        <v>3871200</v>
       </c>
       <c r="G81" s="3">
-        <v>2622000</v>
+        <v>2782100</v>
       </c>
       <c r="H81" s="3">
-        <v>3103400</v>
+        <v>3250500</v>
       </c>
       <c r="I81" s="3">
-        <v>3185900</v>
+        <v>3171800</v>
       </c>
       <c r="J81" s="3">
-        <v>4036800</v>
+        <v>4372900</v>
       </c>
       <c r="K81" s="3">
         <v>2646300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1337500</v>
+        <v>1375900</v>
       </c>
       <c r="E83" s="3">
-        <v>1272700</v>
+        <v>1277500</v>
       </c>
       <c r="F83" s="3">
-        <v>1176300</v>
+        <v>1262800</v>
       </c>
       <c r="G83" s="3">
-        <v>1169700</v>
+        <v>1247100</v>
       </c>
       <c r="H83" s="3">
-        <v>1149800</v>
+        <v>1204300</v>
       </c>
       <c r="I83" s="3">
-        <v>978300</v>
+        <v>974000</v>
       </c>
       <c r="J83" s="3">
-        <v>943000</v>
+        <v>1021500</v>
       </c>
       <c r="K83" s="3">
         <v>890600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5127000</v>
+        <v>5274000</v>
       </c>
       <c r="E89" s="3">
-        <v>4907600</v>
+        <v>4926000</v>
       </c>
       <c r="F89" s="3">
-        <v>5131400</v>
+        <v>5508500</v>
       </c>
       <c r="G89" s="3">
-        <v>4538100</v>
+        <v>4838300</v>
       </c>
       <c r="H89" s="3">
-        <v>4360000</v>
+        <v>4566600</v>
       </c>
       <c r="I89" s="3">
-        <v>4356300</v>
+        <v>4337000</v>
       </c>
       <c r="J89" s="3">
-        <v>4060400</v>
+        <v>4398400</v>
       </c>
       <c r="K89" s="3">
         <v>3781900</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2346000</v>
+        <v>-2413200</v>
       </c>
       <c r="E91" s="3">
-        <v>-2024300</v>
+        <v>-2031900</v>
       </c>
       <c r="F91" s="3">
-        <v>-2128100</v>
+        <v>-2284500</v>
       </c>
       <c r="G91" s="3">
-        <v>-2107500</v>
+        <v>-2246900</v>
       </c>
       <c r="H91" s="3">
-        <v>-2845100</v>
+        <v>-2979900</v>
       </c>
       <c r="I91" s="3">
-        <v>-2599200</v>
+        <v>-2587700</v>
       </c>
       <c r="J91" s="3">
-        <v>-1967600</v>
+        <v>-2131400</v>
       </c>
       <c r="K91" s="3">
         <v>-1959300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2552800</v>
+        <v>-2626000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1847600</v>
+        <v>-1854600</v>
       </c>
       <c r="F94" s="3">
-        <v>-2114800</v>
+        <v>-2270300</v>
       </c>
       <c r="G94" s="3">
-        <v>-2168600</v>
+        <v>-2312000</v>
       </c>
       <c r="H94" s="3">
-        <v>-3084300</v>
+        <v>-3230400</v>
       </c>
       <c r="I94" s="3">
-        <v>-2505700</v>
+        <v>-2494600</v>
       </c>
       <c r="J94" s="3">
-        <v>-2015500</v>
+        <v>-2183300</v>
       </c>
       <c r="K94" s="3">
         <v>-1949800</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1524500</v>
+        <v>1568200</v>
       </c>
       <c r="E96" s="3">
-        <v>-1475200</v>
+        <v>1480700</v>
       </c>
       <c r="F96" s="3">
-        <v>-1280800</v>
+        <v>1375000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1202800</v>
+        <v>1282400</v>
       </c>
       <c r="H96" s="3">
-        <v>-1136600</v>
+        <v>1190400</v>
       </c>
       <c r="I96" s="3">
-        <v>-981200</v>
+        <v>976900</v>
       </c>
       <c r="J96" s="3">
-        <v>-912000</v>
+        <v>988000</v>
       </c>
       <c r="K96" s="3">
         <v>-842600</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2507200</v>
+        <v>-2579100</v>
       </c>
       <c r="E100" s="3">
-        <v>-3435400</v>
+        <v>-3448300</v>
       </c>
       <c r="F100" s="3">
-        <v>-2839200</v>
+        <v>-3047800</v>
       </c>
       <c r="G100" s="3">
-        <v>-1992600</v>
+        <v>-2124500</v>
       </c>
       <c r="H100" s="3">
-        <v>-1400800</v>
+        <v>-1467200</v>
       </c>
       <c r="I100" s="3">
-        <v>-1698900</v>
+        <v>-1691400</v>
       </c>
       <c r="J100" s="3">
-        <v>-2131000</v>
+        <v>-2308500</v>
       </c>
       <c r="K100" s="3">
         <v>-1845900</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="E101" s="3">
         <v>2200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+        <v>-800</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J101" s="3">
-        <v>-1500</v>
+        <v>-1600</v>
       </c>
       <c r="K101" s="3">
         <v>10900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>66200</v>
+        <v>68100</v>
       </c>
       <c r="E102" s="3">
-        <v>-373200</v>
+        <v>-374600</v>
       </c>
       <c r="F102" s="3">
-        <v>177400</v>
+        <v>190400</v>
       </c>
       <c r="G102" s="3">
-        <v>376900</v>
+        <v>401800</v>
       </c>
       <c r="H102" s="3">
-        <v>-125900</v>
+        <v>-131800</v>
       </c>
       <c r="I102" s="3">
-        <v>151600</v>
+        <v>151000</v>
       </c>
       <c r="J102" s="3">
-        <v>-87600</v>
+        <v>-94900</v>
       </c>
       <c r="K102" s="3">
         <v>-2900</v>

--- a/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>CNI</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11847000</v>
+      </c>
+      <c r="E8" s="3">
         <v>12742400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12639800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11439800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10845200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11500800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10495100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10398900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8751000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9469100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9525800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8140800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7382600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6935600</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5374500</v>
+      </c>
+      <c r="E9" s="3">
         <v>5589000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5529700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5028900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4839900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5333700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4930600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4601000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1921500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2263100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2703700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2286400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2063000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1945200</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6472600</v>
+      </c>
+      <c r="E10" s="3">
         <v>7153400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7110100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6411000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6005300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6167100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5564500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5797900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6829500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7206000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6822100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5854500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5319600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4990400</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,41 +979,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-103000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-745200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>771500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>364700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-260200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-17500</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1008,54 +1027,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1314900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1375900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1277500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1262800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1247100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1204300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>974000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1021500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>890600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>869500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>824300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>754400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>687700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>679100</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7135600</v>
+      </c>
+      <c r="E17" s="3">
         <v>7384400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7218000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6691500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6087000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6538000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6248300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5966900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5092700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5515100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5895700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5159300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4640100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4403500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4711400</v>
+      </c>
+      <c r="E18" s="3">
         <v>5358000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5421800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4748400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4758300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4962900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4246900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4431900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3658300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3954000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3630100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2981500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2742400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2532100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9600</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>272600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>35300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>84000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>56200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>234400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>308100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6041700</v>
+      </c>
+      <c r="E21" s="3">
         <v>6732400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6689700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6011100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6001400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6169500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5236200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5445400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4826500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4845500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4535300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3790800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3665900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3522500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>619200</v>
+      </c>
+      <c r="E22" s="3">
         <v>546700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>404900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>482000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>434800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>414800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>358400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>383500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>349000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>329600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>291300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>274800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>254500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>262000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4067200</v>
+      </c>
+      <c r="E23" s="3">
         <v>4912800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4997000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5011500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3548100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4185700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4164000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4058000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3582000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3659700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3422800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2762900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2722300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2578200</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>975800</v>
+      </c>
+      <c r="E24" s="3">
         <v>653500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1215400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1140300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>766000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>935200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>992300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-315000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>935700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1003100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>936600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>752100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>727800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>690600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3091400</v>
+      </c>
+      <c r="E26" s="3">
         <v>4259300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3781500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3871200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2782100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3250500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3171800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4372900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2646300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2656500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2486300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2010800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1994500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1887500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3091400</v>
+      </c>
+      <c r="E27" s="3">
         <v>4259300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3781500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3871200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2782100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3250500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3171800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4372900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2646300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2656500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2486300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2010800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1994500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1887500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,8 +1670,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9600</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-272600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-35300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-84000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-56200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-234400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-308100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3091400</v>
+      </c>
+      <c r="E33" s="3">
         <v>4259300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3781500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3871200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2782100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3250500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3171800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4372900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2646300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2656500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2486300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2010800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1994500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1887500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3091400</v>
+      </c>
+      <c r="E35" s="3">
         <v>4259300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3781500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3871200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2782100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3250500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3171800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4372900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2646300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2656500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2486300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2010800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1994500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1887500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>270400</v>
+      </c>
+      <c r="E41" s="3">
         <v>359700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>242300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>662200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>446600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>194900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>128000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>114900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>164700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>115400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>77600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,324 +2165,348 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>908400</v>
+      </c>
+      <c r="E43" s="3">
         <v>984400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1047000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>848700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>893900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1104100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>856700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>784600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>636100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>659300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>728500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>627400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>618400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>629900</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>500400</v>
+      </c>
+      <c r="E44" s="3">
         <v>529300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>511300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>465400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>457500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>471100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>408200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>338100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>258100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>266600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>263000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>210900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>171200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>154400</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E45" s="3">
         <v>25000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>65000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>221300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>103600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>43900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>178100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>182600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>509600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>575900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>660200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>518900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>486000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>557700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1820200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2339000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2376900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2707300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2434500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2181900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1999200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1746300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1531800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1616600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1564600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1521900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1390900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1419700</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>297500</v>
+      </c>
+      <c r="E47" s="3">
         <v>304400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>69500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>94000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>65100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>64800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>51300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>58200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>73400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>159900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>156200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>136300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>87100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>99100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32510200</v>
+      </c>
+      <c r="E48" s="3">
         <v>32933500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31396800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31742600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30700800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29995300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26869100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26653000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24540200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24496100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22384900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20190100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18263700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18373800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1297600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1324400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1271600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1313300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1255700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1166500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>866200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>658700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>48700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>53300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>48700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>42400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>41500</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3175500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2398900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2269100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2451200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>656100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>296800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>373000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>840500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>746600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1006900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>721500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2614300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>59900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39661800</v>
+      </c>
+      <c r="E54" s="3">
         <v>39879500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37432600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38355100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35162500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33757000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30203600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30005300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26940800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27332800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24875900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23220100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19839900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19994000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>716500</v>
+      </c>
+      <c r="E57" s="3">
         <v>733000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>704900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>713600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>612100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>667700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>719700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>588500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1103600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1166800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1451100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>287300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>341900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>903500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1860500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>873300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>486800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>798100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1582100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>867700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1658600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1082500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1082700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>427100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>786000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>429400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>103700</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>389900</v>
+      </c>
+      <c r="E59" s="3">
         <v>456600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>463300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>511300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>481100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>426400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>343000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>345300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>822900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>922800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>871900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2763300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3812600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2838700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2465400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2569500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3305200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2565000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3176000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2186800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2251100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1727900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1923000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1639500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1317500</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13949400</v>
+      </c>
+      <c r="E61" s="3">
         <v>12441800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10871000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9718800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9658600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9440800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8343500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6975600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6868800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6746500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6145400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5249400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4705600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4948200</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>296100</v>
+      </c>
+      <c r="E62" s="3">
         <v>333200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>314000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>337400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>352400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>364700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>367200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>470500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7095600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7109900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6428000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6886000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5295100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5523600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25031300</v>
+      </c>
+      <c r="E66" s="3">
         <v>24646600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21632600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20382600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19740200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19847600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17275400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16723800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16151300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16107400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14301300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13248600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11640200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11789300</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12756100</v>
+      </c>
+      <c r="E72" s="3">
         <v>14125800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14429400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16584100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15037700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13595600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12182100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12408300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9627100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9488600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9216500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8304800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7566400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7204500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14630500</v>
+      </c>
+      <c r="E76" s="3">
         <v>15232900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15800000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17972500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15422200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13909400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12928200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13281400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10789600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11225400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10574600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9971500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8199700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8204700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3091400</v>
+      </c>
+      <c r="E81" s="3">
         <v>4259300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3781500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3871200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2782100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3250500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3171800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4372900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2646300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2656500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2486300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2010800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1994500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1887500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1314900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1375900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1277500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1262800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1247100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1204300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>974000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1021500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>890600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>869500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>824300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>754400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>687700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>679100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4655800</v>
+      </c>
+      <c r="E89" s="3">
         <v>5274000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4926000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5508500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4838300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4566600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4337000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4398400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3781900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3859400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3439300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2731300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2277300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2286300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2466600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2413200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2031900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2284500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2246900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2979900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2587700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2131400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1959300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2031800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1803300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1518900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1288200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1248400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2506900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2626000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1854600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2270300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2312000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3230400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2494600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2183300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1949800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2122700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1708300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1425700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1057500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1328300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1485900</v>
+      </c>
+      <c r="E96" s="3">
         <v>1568200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1480700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1375000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1282400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1190400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>976900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>988000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-842600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-747900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-642200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-557300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-485200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-449400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2515900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2579100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3448300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3047800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2124500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1467200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1691400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2308500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1845900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1669200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1860600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1274800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1177300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1267600</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2200</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>10900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>14600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>10800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-363500</v>
+      </c>
+      <c r="E102" s="3">
         <v>68100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-374600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>190400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>401800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-131800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>151000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-94900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>75800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-127200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>45400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-298800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>CNI</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12620300</v>
+      </c>
+      <c r="E8" s="3">
         <v>11847000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12742400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12639800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11439800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10845200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11500800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10495100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10398900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8751000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9469100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9525800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8140800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7382600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6935600</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5468500</v>
+      </c>
+      <c r="E9" s="3">
         <v>5374500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5589000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5529700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5028900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4839900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5333700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4930600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4601000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1921500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2263100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2703700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2286400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2063000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1945200</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7151800</v>
+      </c>
+      <c r="E10" s="3">
         <v>6472600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7153400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7110100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6411000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6005300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6167100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5564500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5797900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6829500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7206000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6822100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5854500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5319600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4990400</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,44 +998,47 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E14" s="3">
         <v>40300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-103000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-745200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>771500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>364700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-260200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-17500</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1030,57 +1049,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1413400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1314900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1375900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1277500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1262800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1247100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1204300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>974000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1021500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>890600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>869500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>824300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>754400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>687700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>679100</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7425300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7135600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7384400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7218000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6691500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6087000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6538000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6248300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5966900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5092700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5515100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5895700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5159300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4640100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4403500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5195000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4711400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5358000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5421800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4748400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4758300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4962900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4246900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4431900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3658300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3954000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3630100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2981500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2742400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2532100</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>272600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>35300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>84000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>56200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>234400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>308100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6620100</v>
+      </c>
+      <c r="E21" s="3">
         <v>6041700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6732400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6689700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6011100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6001400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6169500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5236200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5445400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4826500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4845500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4535300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3790800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3665900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3522500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>665900</v>
+      </c>
+      <c r="E22" s="3">
         <v>619200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>546700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>404900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>482000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>434800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>414800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>358400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>383500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>349000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>329600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>291300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>274800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>254500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>262000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4568500</v>
+      </c>
+      <c r="E23" s="3">
         <v>4067200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4912800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4997000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5011500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3548100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4185700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4164000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4058000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3582000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3659700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3422800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2762900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2722300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2578200</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1126100</v>
+      </c>
+      <c r="E24" s="3">
         <v>975800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>653500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1215400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1140300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>766000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>935200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>992300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-315000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>935700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1003100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>936600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>752100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>727800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>690600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3442400</v>
+      </c>
+      <c r="E26" s="3">
         <v>3091400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4259300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3781500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3871200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2782100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3250500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3171800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4372900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2646300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2656500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2486300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2010800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1994500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1887500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3442400</v>
+      </c>
+      <c r="E27" s="3">
         <v>3091400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4259300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3781500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3871200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2782100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3250500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3171800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4372900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2646300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2656500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2486300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2010800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1994500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1887500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1733,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E32" s="3">
         <v>15300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-272600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-35300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-84000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-56200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-234400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-308100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3442400</v>
+      </c>
+      <c r="E33" s="3">
         <v>3091400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4259300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3781500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3871200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2782100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3250500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3171800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4372900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2646300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2656500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2486300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2010800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1994500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1887500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3442400</v>
+      </c>
+      <c r="E35" s="3">
         <v>3091400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4259300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3781500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3871200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2782100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3250500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3171800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4372900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2646300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2656500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2486300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2010800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1994500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1887500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>255300</v>
+      </c>
+      <c r="E41" s="3">
         <v>270400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>359700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>242300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>662200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>446600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>194900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>55800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>128000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>114900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>164700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>115400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>77600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2168,345 +2257,369 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>814700</v>
+      </c>
+      <c r="E43" s="3">
         <v>908400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>984400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1047000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>848700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>893900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1104100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>856700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>784600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>636100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>659300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>728500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>627400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>618400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>629900</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>535300</v>
+      </c>
+      <c r="E44" s="3">
         <v>500400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>529300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>511300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>465400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>457500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>471100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>408200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>338100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>258100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>266600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>263000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>210900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>171200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>154400</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E45" s="3">
         <v>54200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>65000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>221300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>103600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>43900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>178100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>182600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>509600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>575900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>660200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>518900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>486000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>557700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1802200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1820200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2339000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2376900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2707300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2434500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2181900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1999200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1746300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1531800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1616600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1564600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1521900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1390900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1419700</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E47" s="3">
         <v>297500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>304400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>69500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>94000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>51300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>58200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>73400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>159900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>156200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>136300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>87100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>99100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34940800</v>
+      </c>
+      <c r="E48" s="3">
         <v>32510200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32933500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31396800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31742600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30700800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29995300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26869100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26653000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24540200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24496100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22384900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20190100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18263700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18373800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1385700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1297600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1324400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1271600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1313300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1255700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1166500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>866200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>658700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>48700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>53300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>48700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>45400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>42400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>41500</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3950800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3175500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2398900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2269100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2451200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>656100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>296800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>373000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>840500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>746600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1006900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>721500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2614300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>59900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42706000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39661800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39879500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37432600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38355100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>35162500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33757000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30203600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30005300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26940800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27332800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24875900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23220100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19839900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19994000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>649100</v>
+      </c>
+      <c r="E57" s="3">
         <v>716500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>733000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>704900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>713600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>612100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>667700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>719700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>588500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1103600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1166800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1451100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>287300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>341900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>739500</v>
+      </c>
+      <c r="E58" s="3">
         <v>903500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1860500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>873300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>486800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>798100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1582100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>867700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1658600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1082500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1082700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>427100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>786000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>429400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>103700</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E59" s="3">
         <v>389900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>456600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>463300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>511300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>481100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>426400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>343000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>345300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3" t="s">
+      <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>822900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>922800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>871900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2695600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2763300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3812600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2838700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2465400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2569500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3305200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2565000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3176000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2186800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2251100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1727900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1923000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1639500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1317500</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15035900</v>
+      </c>
+      <c r="E61" s="3">
         <v>13949400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12441800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10871000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9718800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9658600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9440800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8343500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6975600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6868800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6746500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6145400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5249400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4705600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4948200</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>349300</v>
+      </c>
+      <c r="E62" s="3">
         <v>296100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>333200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>314000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>337400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>352400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>364700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>367200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>470500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7095600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7109900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6428000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6886000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5295100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5523600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26975800</v>
+      </c>
+      <c r="E66" s="3">
         <v>25031300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24646600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21632600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20382600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19740200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19847600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17275400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16723800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16151300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16107400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14301300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13248600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11640200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11789300</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13797500</v>
+      </c>
+      <c r="E72" s="3">
         <v>12756100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14125800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14429400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16584100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15037700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13595600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12182100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12408300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9627100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9488600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9216500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8304800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7566400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7204500</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15730200</v>
+      </c>
+      <c r="E76" s="3">
         <v>14630500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15232900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15800000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17972500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15422200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13909400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12928200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13281400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10789600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11225400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10574600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9971500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8199700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8204700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3442400</v>
+      </c>
+      <c r="E81" s="3">
         <v>3091400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4259300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3781500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3871200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2782100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3250500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3171800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4372900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2646300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2656500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2486300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2010800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1994500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1887500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1413400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1314900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1375900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1277500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1262800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1247100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1204300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>974000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1021500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>890600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>869500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>824300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>754400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>687700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>679100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5141100</v>
+      </c>
+      <c r="E89" s="3">
         <v>4655800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5274000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4926000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5508500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4838300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4566600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4337000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4398400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3781900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3859400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3439300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2731300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2277300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2286300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2667900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2466600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2413200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2031900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2284500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2246900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2979900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2587700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2131400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1959300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2031800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1803300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1518900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1288200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1248400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2708000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2506900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2626000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1854600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2270300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2312000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3230400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2494600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2183300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1949800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2122700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1708300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1425700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1057500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1328300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1610400</v>
+      </c>
+      <c r="E96" s="3">
         <v>1485900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1568200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1480700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1375000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1282400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1190400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>976900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>988000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-842600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-747900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-642200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-557300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-485200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-449400</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2458600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2515900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2579100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3448300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3047800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2124500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1467200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1691400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2308500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1845900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1669200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1860600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1274800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1177300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1267600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E101" s="3">
         <v>3500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>10900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>14600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>10800</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-363500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>68100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-374600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>190400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>401800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-131800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>151000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-94900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>75800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-127200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>45400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-298800</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
